--- a/src/data/blogs.xlsx
+++ b/src/data/blogs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Gala\Documents\code\jk3\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5BF936F-BF5A-4544-A992-360978979CC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90DAD24A-1B46-4393-BAE9-C1B9B129FD72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6540F3E8-6E2B-46EF-8B33-43A96A14636B}"/>
+    <workbookView xWindow="84" yWindow="120" windowWidth="11808" windowHeight="11076" xr2:uid="{6540F3E8-6E2B-46EF-8B33-43A96A14636B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3780" uniqueCount="2349">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3780" uniqueCount="2361">
   <si>
     <t>BlogID</t>
   </si>
@@ -6470,9 +6470,6 @@
     <t>ppe,power tools,industrial tools,buying guide</t>
   </si>
   <si>
-    <t>https://images.unsplash.com/photo-1662309376159-b95fb193d96b?w=900&amp;auto=format&amp;fit=crop&amp;q=60&amp;ixlib=rb-4.1.0&amp;ixid=M3wxMjA3fDB8MHxzZWFyY2h8Mnx8SW5kdXN0cmlhbCUyMFNhZmV0eSUyMEVxdWlwbWVudHxlbnwwfHwwfHx8MA%3D%3D</t>
-  </si>
-  <si>
     <t>industrial-safety-equipment-guide.webp</t>
   </si>
   <si>
@@ -6509,9 +6506,6 @@
     <t>kaithal power tools,power tools dealer kaithal,industrial tools,tool shop near me</t>
   </si>
   <si>
-    <t>https://images.unsplash.com/photo-1517048676732-d65bc937f952?w=900</t>
-  </si>
-  <si>
     <t>power-tools-kaithal.webp</t>
   </si>
   <si>
@@ -6569,9 +6563,6 @@
     <t>karnal power tools,power tools dealer karnal,industrial tools</t>
   </si>
   <si>
-    <t>https://images.unsplash.com/photo-1567507145544-da3fe1b4f8f9?w=900</t>
-  </si>
-  <si>
     <t>karnal-tools.webp</t>
   </si>
   <si>
@@ -6626,9 +6617,6 @@
     <t>on grid solar kaithal,solar installer kaithal,net metering</t>
   </si>
   <si>
-    <t>https://images.unsplash.com/photo-1509391366360-2e959784a276?w=900</t>
-  </si>
-  <si>
     <t>solar-kaithal.webp</t>
   </si>
   <si>
@@ -7278,6 +7266,54 @@
   </si>
   <si>
     <t>BLOG0124</t>
+  </si>
+  <si>
+    <t>https://images.unsplash.com/photo-1552879890-3a06dd3a06c2?q=80&amp;w=954&amp;auto=format&amp;fit=crop&amp;ixlib=rb-4.1.0&amp;ixid=M3wxMjA3fDB8MHxwaG90by1wYWdlfHx8fGVufDB8fHx8fA%3D%3D</t>
+  </si>
+  <si>
+    <t>https://images.unsplash.com/photo-1738162837672-de9d735a9b90?q=80&amp;w=1032&amp;auto=format&amp;fit=crop&amp;ixlib=rb-4.1.0&amp;ixid=M3wxMjA3fDB8MHxwaG90by1wYWdlfHx8fGVufDB8fHx8fA%3D%3D</t>
+  </si>
+  <si>
+    <t>https://images.unsplash.com/photo-1519520104014-df63821cb6f9?q=80&amp;w=1170&amp;auto=format&amp;fit=crop&amp;ixlib=rb-4.1.0&amp;ixid=M3wxMjA3fDB8MHxwaG90by1wYWdlfHx8fGVufDB8fHx8fA%3D%3D</t>
+  </si>
+  <si>
+    <t>https://images.unsplash.com/photo-1590282876176-efa60bc0e782?q=80&amp;w=1074&amp;auto=format&amp;fit=crop&amp;ixlib=rb-4.1.0&amp;ixid=M3wxMjA3fDB8MHxwaG90by1wYWdlfHx8fGVufDB8fHx8fA%3D%3D</t>
+  </si>
+  <si>
+    <t>https://images.unsplash.com/photo-1663948138866-cd74128c1b1e?q=80&amp;w=933&amp;auto=format&amp;fit=crop&amp;ixlib=rb-4.1.0&amp;ixid=M3wxMjA3fDB8MHxwaG90by1wYWdlfHx8fGVufDB8fHx8fA%3D%3D</t>
+  </si>
+  <si>
+    <t>https://images.unsplash.com/photo-1751486403850-fae53b6ab0e5?q=80&amp;w=1170&amp;auto=format&amp;fit=crop&amp;ixlib=rb-4.1.0&amp;ixid=M3wxMjA3fDB8MHxwaG90by1wYWdlfHx8fGVufDB8fHx8fA%3D%3D</t>
+  </si>
+  <si>
+    <t>https://images.unsplash.com/photo-1733024083848-16691c886417?q=80&amp;w=1170&amp;auto=format&amp;fit=crop&amp;ixlib=rb-4.1.0&amp;ixid=M3wxMjA3fDB8MHxwaG90by1wYWdlfHx8fGVufDB8fHx8fA%3D%3D</t>
+  </si>
+  <si>
+    <t>https://images.unsplash.com/photo-1783309239756-168e747dde35?q=80&amp;w=1171&amp;auto=format&amp;fit=crop&amp;ixlib=rb-4.1.0&amp;ixid=M3wxMjA3fDB8MHxwaG90by1wYWdlfHx8fGVufDB8fHx8fA%3D%3D</t>
+  </si>
+  <si>
+    <t>https://images.unsplash.com/photo-1542238060-646c7ed65622?q=80&amp;w=1170&amp;auto=format&amp;fit=crop&amp;ixlib=rb-4.1.0&amp;ixid=M3wxMjA3fDB8MHxwaG90by1wYWdlfHx8fGVufDB8fHx8fA%3D%3D</t>
+  </si>
+  <si>
+    <t>https://images.unsplash.com/photo-1767389193137-77d6f9b8b56a?q=80&amp;w=1170&amp;auto=format&amp;fit=crop&amp;ixlib=rb-4.1.0&amp;ixid=M3wxMjA3fDB8MHxwaG90by1wYWdlfHx8fGVufDB8fHx8fA%3D%3D</t>
+  </si>
+  <si>
+    <t>https://images.unsplash.com/photo-1783587354869-de09cfffaf9a?q=80&amp;w=1174&amp;auto=format&amp;fit=crop&amp;ixlib=rb-4.1.0&amp;ixid=M3wxMjA3fDB8MHxwaG90by1wYWdlfHx8fGVufDB8fHx8fA%3D%3D</t>
+  </si>
+  <si>
+    <t>https://images.unsplash.com/photo-1617269778723-73a40cf299bd?q=80&amp;w=1170&amp;auto=format&amp;fit=crop&amp;ixlib=rb-4.1.0&amp;ixid=M3wxMjA3fDB8MHxwaG90by1wYWdlfHx8fGVufDB8fHx8fA%3D%3D</t>
+  </si>
+  <si>
+    <t>https://images.unsplash.com/photo-1502637098811-fa9526d2b659?q=80&amp;w=1032&amp;auto=format&amp;fit=crop&amp;ixlib=rb-4.1.0&amp;ixid=M3wxMjA3fDB8MHxwaG90by1wYWdlfHx8fGVufDB8fHx8fA%3D%3D</t>
+  </si>
+  <si>
+    <t>https://images.unsplash.com/photo-1694327671725-e2a81cda3436?q=80&amp;w=1170&amp;auto=format&amp;fit=crop&amp;ixlib=rb-4.1.0&amp;ixid=M3wxMjA3fDB8MHxwaG90by1wYWdlfHx8fGVufDB8fHx8fA%3D%3D</t>
+  </si>
+  <si>
+    <t>https://images.unsplash.com/photo-1463173904305-ba479d2123b7?q=80&amp;w=958&amp;auto=format&amp;fit=crop&amp;ixlib=rb-4.1.0&amp;ixid=M3wxMjA3fDB8MHxwaG90by1wYWdlfHx8fGVufDB8fHx8fA%3D%3D</t>
+  </si>
+  <si>
+    <t>https://images.unsplash.com/photo-1680355065203-43ad84bb6e69?q=80&amp;w=965&amp;auto=format&amp;fit=crop&amp;ixlib=rb-4.1.0&amp;ixid=M3wxMjA3fDB8MHxwaG90by1wYWdlfHx8fGVufDB8fHx8fA%3D%3D</t>
   </si>
 </sst>
 </file>
@@ -7354,7 +7390,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -7366,6 +7402,8 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
@@ -7702,7 +7740,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A8F2F70-D1BF-44E2-90B8-B0E4DAB2F558}">
-  <dimension ref="A1:AK127"/>
+  <dimension ref="A1:AK125"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="9" max="9" width="11.5546875" style="8" bestFit="1" customWidth="1"/>
@@ -17808,11 +17846,11 @@
       <c r="AA91" s="3" t="s">
         <v>1841</v>
       </c>
-      <c r="AB91" s="9" t="s">
+      <c r="AB91" s="11" t="s">
         <v>1488</v>
       </c>
-      <c r="AC91" s="10"/>
-      <c r="AD91" s="10"/>
+      <c r="AC91" s="12"/>
+      <c r="AD91" s="12"/>
       <c r="AE91" s="5" t="s">
         <v>1847</v>
       </c>
@@ -17917,11 +17955,11 @@
       <c r="AA92" s="3" t="s">
         <v>1855</v>
       </c>
-      <c r="AB92" s="9" t="s">
+      <c r="AB92" s="11" t="s">
         <v>1488</v>
       </c>
-      <c r="AC92" s="10"/>
-      <c r="AD92" s="10"/>
+      <c r="AC92" s="12"/>
+      <c r="AD92" s="12"/>
       <c r="AE92" s="5" t="s">
         <v>1861</v>
       </c>
@@ -18026,11 +18064,11 @@
       <c r="AA93" s="3" t="s">
         <v>1869</v>
       </c>
-      <c r="AB93" s="9" t="s">
+      <c r="AB93" s="11" t="s">
         <v>1488</v>
       </c>
-      <c r="AC93" s="10"/>
-      <c r="AD93" s="10"/>
+      <c r="AC93" s="12"/>
+      <c r="AD93" s="12"/>
       <c r="AE93" s="5" t="s">
         <v>1875</v>
       </c>
@@ -18135,11 +18173,11 @@
       <c r="AA94" s="3" t="s">
         <v>1881</v>
       </c>
-      <c r="AB94" s="9" t="s">
+      <c r="AB94" s="11" t="s">
         <v>1488</v>
       </c>
-      <c r="AC94" s="10"/>
-      <c r="AD94" s="10"/>
+      <c r="AC94" s="12"/>
+      <c r="AD94" s="12"/>
       <c r="AE94" s="5" t="s">
         <v>1885</v>
       </c>
@@ -18244,11 +18282,11 @@
       <c r="AA95" s="3" t="s">
         <v>1881</v>
       </c>
-      <c r="AB95" s="9" t="s">
+      <c r="AB95" s="11" t="s">
         <v>1488</v>
       </c>
-      <c r="AC95" s="10"/>
-      <c r="AD95" s="10"/>
+      <c r="AC95" s="12"/>
+      <c r="AD95" s="12"/>
       <c r="AE95" s="5" t="s">
         <v>1894</v>
       </c>
@@ -18353,11 +18391,11 @@
       <c r="AA96" s="3" t="s">
         <v>1902</v>
       </c>
-      <c r="AB96" s="9" t="s">
+      <c r="AB96" s="11" t="s">
         <v>1488</v>
       </c>
-      <c r="AC96" s="10"/>
-      <c r="AD96" s="10"/>
+      <c r="AC96" s="12"/>
+      <c r="AD96" s="12"/>
       <c r="AE96" s="5" t="s">
         <v>1908</v>
       </c>
@@ -18462,11 +18500,11 @@
       <c r="AA97" s="3" t="s">
         <v>1916</v>
       </c>
-      <c r="AB97" s="9" t="s">
+      <c r="AB97" s="11" t="s">
         <v>1488</v>
       </c>
-      <c r="AC97" s="10"/>
-      <c r="AD97" s="10"/>
+      <c r="AC97" s="12"/>
+      <c r="AD97" s="12"/>
       <c r="AE97" s="5" t="s">
         <v>1922</v>
       </c>
@@ -18571,11 +18609,11 @@
       <c r="AA98" s="3" t="s">
         <v>1928</v>
       </c>
-      <c r="AB98" s="9" t="s">
+      <c r="AB98" s="11" t="s">
         <v>1488</v>
       </c>
-      <c r="AC98" s="10"/>
-      <c r="AD98" s="10"/>
+      <c r="AC98" s="12"/>
+      <c r="AD98" s="12"/>
       <c r="AE98" s="5" t="s">
         <v>1932</v>
       </c>
@@ -18680,11 +18718,11 @@
       <c r="AA99" s="3" t="s">
         <v>1939</v>
       </c>
-      <c r="AB99" s="9" t="s">
+      <c r="AB99" s="11" t="s">
         <v>1488</v>
       </c>
-      <c r="AC99" s="10"/>
-      <c r="AD99" s="10"/>
+      <c r="AC99" s="12"/>
+      <c r="AD99" s="12"/>
       <c r="AE99" s="5" t="s">
         <v>1945</v>
       </c>
@@ -18789,11 +18827,11 @@
       <c r="AA100" s="3" t="s">
         <v>1952</v>
       </c>
-      <c r="AB100" s="9" t="s">
+      <c r="AB100" s="11" t="s">
         <v>1488</v>
       </c>
-      <c r="AC100" s="10"/>
-      <c r="AD100" s="10"/>
+      <c r="AC100" s="12"/>
+      <c r="AD100" s="12"/>
       <c r="AE100" s="5" t="s">
         <v>1958</v>
       </c>
@@ -18898,11 +18936,11 @@
       <c r="AA101" s="3" t="s">
         <v>1966</v>
       </c>
-      <c r="AB101" s="9" t="s">
+      <c r="AB101" s="11" t="s">
         <v>1488</v>
       </c>
-      <c r="AC101" s="10"/>
-      <c r="AD101" s="10"/>
+      <c r="AC101" s="12"/>
+      <c r="AD101" s="12"/>
       <c r="AE101" s="5" t="s">
         <v>1972</v>
       </c>
@@ -19007,11 +19045,11 @@
       <c r="AA102" s="3" t="s">
         <v>1979</v>
       </c>
-      <c r="AB102" s="9" t="s">
+      <c r="AB102" s="11" t="s">
         <v>1488</v>
       </c>
-      <c r="AC102" s="10"/>
-      <c r="AD102" s="10"/>
+      <c r="AC102" s="12"/>
+      <c r="AD102" s="12"/>
       <c r="AE102" s="5" t="s">
         <v>1985</v>
       </c>
@@ -19116,11 +19154,11 @@
       <c r="AA103" s="3" t="s">
         <v>1991</v>
       </c>
-      <c r="AB103" s="9" t="s">
+      <c r="AB103" s="11" t="s">
         <v>1488</v>
       </c>
-      <c r="AC103" s="10"/>
-      <c r="AD103" s="10"/>
+      <c r="AC103" s="12"/>
+      <c r="AD103" s="12"/>
       <c r="AE103" s="5" t="s">
         <v>1995</v>
       </c>
@@ -19225,11 +19263,11 @@
       <c r="AA104" s="3" t="s">
         <v>2002</v>
       </c>
-      <c r="AB104" s="9" t="s">
+      <c r="AB104" s="11" t="s">
         <v>1488</v>
       </c>
-      <c r="AC104" s="10"/>
-      <c r="AD104" s="10"/>
+      <c r="AC104" s="12"/>
+      <c r="AD104" s="12"/>
       <c r="AE104" s="5" t="s">
         <v>2008</v>
       </c>
@@ -19334,11 +19372,11 @@
       <c r="AA105" s="3" t="s">
         <v>2013</v>
       </c>
-      <c r="AB105" s="9" t="s">
+      <c r="AB105" s="11" t="s">
         <v>1488</v>
       </c>
-      <c r="AC105" s="10"/>
-      <c r="AD105" s="10"/>
+      <c r="AC105" s="12"/>
+      <c r="AD105" s="12"/>
       <c r="AE105" s="5" t="s">
         <v>2017</v>
       </c>
@@ -19443,11 +19481,11 @@
       <c r="AA106" s="3" t="s">
         <v>2025</v>
       </c>
-      <c r="AB106" s="9" t="s">
+      <c r="AB106" s="11" t="s">
         <v>1488</v>
       </c>
-      <c r="AC106" s="10"/>
-      <c r="AD106" s="10"/>
+      <c r="AC106" s="12"/>
+      <c r="AD106" s="12"/>
       <c r="AE106" s="5" t="s">
         <v>2031</v>
       </c>
@@ -19552,11 +19590,11 @@
       <c r="AA107" s="3" t="s">
         <v>2039</v>
       </c>
-      <c r="AB107" s="9" t="s">
+      <c r="AB107" s="11" t="s">
         <v>1488</v>
       </c>
-      <c r="AC107" s="10"/>
-      <c r="AD107" s="10"/>
+      <c r="AC107" s="12"/>
+      <c r="AD107" s="12"/>
       <c r="AE107" s="5" t="s">
         <v>2045</v>
       </c>
@@ -19661,11 +19699,11 @@
       <c r="AA108" s="3" t="s">
         <v>2053</v>
       </c>
-      <c r="AB108" s="9" t="s">
+      <c r="AB108" s="11" t="s">
         <v>1488</v>
       </c>
-      <c r="AC108" s="10"/>
-      <c r="AD108" s="10"/>
+      <c r="AC108" s="12"/>
+      <c r="AD108" s="12"/>
       <c r="AE108" s="5" t="s">
         <v>2059</v>
       </c>
@@ -19770,11 +19808,11 @@
       <c r="AA109" s="3" t="s">
         <v>2068</v>
       </c>
-      <c r="AB109" s="9" t="s">
+      <c r="AB109" s="11" t="s">
         <v>1488</v>
       </c>
-      <c r="AC109" s="10"/>
-      <c r="AD109" s="10"/>
+      <c r="AC109" s="12"/>
+      <c r="AD109" s="12"/>
       <c r="AE109" s="5" t="s">
         <v>2074</v>
       </c>
@@ -19834,41 +19872,41 @@
       <c r="L110" s="4">
         <v>5</v>
       </c>
-      <c r="M110" s="5" t="s">
+      <c r="M110" s="9" t="s">
+        <v>2345</v>
+      </c>
+      <c r="N110" s="3" t="s">
         <v>2079</v>
-      </c>
-      <c r="N110" s="3" t="s">
-        <v>2080</v>
       </c>
       <c r="O110" s="3" t="s">
         <v>2077</v>
       </c>
       <c r="P110" s="3" t="s">
+        <v>2080</v>
+      </c>
+      <c r="Q110" s="5" t="s">
         <v>2081</v>
       </c>
-      <c r="Q110" s="5" t="s">
+      <c r="R110" s="3" t="s">
         <v>2082</v>
       </c>
-      <c r="R110" s="3" t="s">
+      <c r="S110" s="3" t="s">
+        <v>2080</v>
+      </c>
+      <c r="T110" s="3" t="s">
         <v>2083</v>
       </c>
-      <c r="S110" s="3" t="s">
-        <v>2081</v>
-      </c>
-      <c r="T110" s="3" t="s">
+      <c r="U110" s="3" t="s">
         <v>2084</v>
       </c>
-      <c r="U110" s="3" t="s">
+      <c r="V110" s="5" t="s">
         <v>2085</v>
-      </c>
-      <c r="V110" s="5" t="s">
-        <v>2086</v>
       </c>
       <c r="W110" s="3" t="s">
         <v>2077</v>
       </c>
       <c r="X110" s="3" t="s">
-        <v>2081</v>
+        <v>2080</v>
       </c>
       <c r="Y110" s="5" t="s">
         <v>1488</v>
@@ -19877,15 +19915,15 @@
         <v>2077</v>
       </c>
       <c r="AA110" s="3" t="s">
-        <v>2081</v>
-      </c>
-      <c r="AB110" s="9" t="s">
+        <v>2080</v>
+      </c>
+      <c r="AB110" s="11" t="s">
         <v>1488</v>
       </c>
-      <c r="AC110" s="10"/>
-      <c r="AD110" s="10"/>
+      <c r="AC110" s="12"/>
+      <c r="AD110" s="12"/>
       <c r="AE110" s="5" t="s">
-        <v>2087</v>
+        <v>2086</v>
       </c>
       <c r="AF110" s="4">
         <v>0.8</v>
@@ -19908,25 +19946,25 @@
     </row>
     <row r="111" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A111" s="1" t="s">
-        <v>2334</v>
+        <v>2330</v>
       </c>
       <c r="B111" s="7" t="s">
+        <v>2087</v>
+      </c>
+      <c r="C111" s="7" t="s">
         <v>2088</v>
-      </c>
-      <c r="C111" s="7" t="s">
-        <v>2089</v>
       </c>
       <c r="D111" s="7" t="s">
         <v>40</v>
       </c>
       <c r="E111" s="7" t="s">
-        <v>2090</v>
+        <v>2089</v>
       </c>
       <c r="F111" s="7" t="s">
         <v>93</v>
       </c>
       <c r="G111" s="7" t="s">
-        <v>2091</v>
+        <v>2090</v>
       </c>
       <c r="H111" s="7" t="s">
         <v>44</v>
@@ -19943,62 +19981,62 @@
       <c r="L111" s="7">
         <v>6</v>
       </c>
-      <c r="M111" s="7" t="s">
+      <c r="M111" s="10" t="s">
+        <v>2347</v>
+      </c>
+      <c r="N111" s="7" t="s">
+        <v>2091</v>
+      </c>
+      <c r="O111" s="7" t="s">
         <v>2092</v>
       </c>
-      <c r="N111" s="7" t="s">
+      <c r="P111" s="7" t="s">
         <v>2093</v>
       </c>
-      <c r="O111" s="7" t="s">
+      <c r="Q111" s="7" t="s">
         <v>2094</v>
       </c>
-      <c r="P111" s="7" t="s">
+      <c r="R111" s="7" t="s">
         <v>2095</v>
       </c>
-      <c r="Q111" s="7" t="s">
+      <c r="S111" s="7" t="s">
         <v>2096</v>
       </c>
-      <c r="R111" s="7" t="s">
+      <c r="T111" s="7" t="s">
         <v>2097</v>
       </c>
-      <c r="S111" s="7" t="s">
+      <c r="U111" s="7" t="s">
         <v>2098</v>
       </c>
-      <c r="T111" s="7" t="s">
+      <c r="V111" s="7" t="s">
         <v>2099</v>
       </c>
-      <c r="U111" s="7" t="s">
+      <c r="W111" s="7" t="s">
         <v>2100</v>
       </c>
-      <c r="V111" s="7" t="s">
+      <c r="X111" s="7" t="s">
         <v>2101</v>
       </c>
-      <c r="W111" s="7" t="s">
+      <c r="Y111" s="7" t="s">
         <v>2102</v>
       </c>
-      <c r="X111" s="7" t="s">
+      <c r="Z111" s="7" t="s">
         <v>2103</v>
       </c>
-      <c r="Y111" s="7" t="s">
+      <c r="AA111" s="7" t="s">
         <v>2104</v>
       </c>
-      <c r="Z111" s="7" t="s">
+      <c r="AB111" s="7" t="s">
+        <v>2102</v>
+      </c>
+      <c r="AC111" s="7" t="s">
         <v>2105</v>
       </c>
-      <c r="AA111" s="7" t="s">
+      <c r="AD111" s="7" t="s">
         <v>2106</v>
       </c>
-      <c r="AB111" s="7" t="s">
-        <v>2104</v>
-      </c>
-      <c r="AC111" s="7" t="s">
+      <c r="AE111" s="7" t="s">
         <v>2107</v>
-      </c>
-      <c r="AD111" s="7" t="s">
-        <v>2108</v>
-      </c>
-      <c r="AE111" s="7" t="s">
-        <v>2109</v>
       </c>
       <c r="AF111" s="7">
         <v>1</v>
@@ -20021,25 +20059,25 @@
     </row>
     <row r="112" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A112" s="1" t="s">
-        <v>2335</v>
+        <v>2331</v>
       </c>
       <c r="B112" s="7" t="s">
+        <v>2106</v>
+      </c>
+      <c r="C112" s="7" t="s">
         <v>2108</v>
-      </c>
-      <c r="C112" s="7" t="s">
-        <v>2110</v>
       </c>
       <c r="D112" s="7" t="s">
         <v>40</v>
       </c>
       <c r="E112" s="7" t="s">
-        <v>2090</v>
+        <v>2089</v>
       </c>
       <c r="F112" s="7" t="s">
         <v>93</v>
       </c>
       <c r="G112" s="7" t="s">
-        <v>2111</v>
+        <v>2109</v>
       </c>
       <c r="H112" s="7" t="s">
         <v>44</v>
@@ -20056,62 +20094,62 @@
       <c r="L112" s="7">
         <v>6</v>
       </c>
-      <c r="M112" s="7" t="s">
+      <c r="M112" s="10" t="s">
+        <v>2346</v>
+      </c>
+      <c r="N112" s="7" t="s">
+        <v>2110</v>
+      </c>
+      <c r="O112" s="7" t="s">
+        <v>2111</v>
+      </c>
+      <c r="P112" s="7" t="s">
         <v>2112</v>
       </c>
-      <c r="N112" s="7" t="s">
+      <c r="Q112" s="7" t="s">
         <v>2113</v>
       </c>
-      <c r="O112" s="7" t="s">
+      <c r="R112" s="7" t="s">
         <v>2114</v>
       </c>
-      <c r="P112" s="7" t="s">
+      <c r="S112" s="7" t="s">
         <v>2115</v>
       </c>
-      <c r="Q112" s="7" t="s">
+      <c r="T112" s="7" t="s">
         <v>2116</v>
       </c>
-      <c r="R112" s="7" t="s">
+      <c r="U112" s="7" t="s">
         <v>2117</v>
       </c>
-      <c r="S112" s="7" t="s">
+      <c r="V112" s="7" t="s">
         <v>2118</v>
       </c>
-      <c r="T112" s="7" t="s">
+      <c r="W112" s="7" t="s">
+        <v>2114</v>
+      </c>
+      <c r="X112" s="7" t="s">
         <v>2119</v>
       </c>
-      <c r="U112" s="7" t="s">
+      <c r="Y112" s="7" t="s">
         <v>2120</v>
       </c>
-      <c r="V112" s="7" t="s">
+      <c r="Z112" s="7" t="s">
         <v>2121</v>
       </c>
-      <c r="W112" s="7" t="s">
-        <v>2117</v>
-      </c>
-      <c r="X112" s="7" t="s">
+      <c r="AA112" s="7" t="s">
         <v>2122</v>
       </c>
-      <c r="Y112" s="7" t="s">
+      <c r="AB112" s="7" t="s">
+        <v>2120</v>
+      </c>
+      <c r="AC112" s="7" t="s">
         <v>2123</v>
       </c>
-      <c r="Z112" s="7" t="s">
+      <c r="AD112" s="7" t="s">
+        <v>2087</v>
+      </c>
+      <c r="AE112" s="7" t="s">
         <v>2124</v>
-      </c>
-      <c r="AA112" s="7" t="s">
-        <v>2125</v>
-      </c>
-      <c r="AB112" s="7" t="s">
-        <v>2123</v>
-      </c>
-      <c r="AC112" s="7" t="s">
-        <v>2126</v>
-      </c>
-      <c r="AD112" s="7" t="s">
-        <v>2088</v>
-      </c>
-      <c r="AE112" s="7" t="s">
-        <v>2127</v>
       </c>
       <c r="AF112" s="7">
         <v>1</v>
@@ -20134,13 +20172,13 @@
     </row>
     <row r="113" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A113" s="1" t="s">
-        <v>2336</v>
+        <v>2332</v>
       </c>
       <c r="B113" s="7" t="s">
-        <v>2128</v>
+        <v>2125</v>
       </c>
       <c r="C113" s="7" t="s">
-        <v>2129</v>
+        <v>2126</v>
       </c>
       <c r="D113" s="7" t="s">
         <v>40</v>
@@ -20152,7 +20190,7 @@
         <v>1494</v>
       </c>
       <c r="G113" s="7" t="s">
-        <v>2130</v>
+        <v>2127</v>
       </c>
       <c r="H113" s="7" t="s">
         <v>44</v>
@@ -20169,58 +20207,58 @@
       <c r="L113" s="7">
         <v>7</v>
       </c>
-      <c r="M113" s="7" t="s">
+      <c r="M113" s="10" t="s">
+        <v>2359</v>
+      </c>
+      <c r="N113" s="7" t="s">
+        <v>2128</v>
+      </c>
+      <c r="O113" s="7" t="s">
+        <v>2129</v>
+      </c>
+      <c r="P113" s="7" t="s">
+        <v>2130</v>
+      </c>
+      <c r="Q113" s="7" t="s">
         <v>2131</v>
       </c>
-      <c r="N113" s="7" t="s">
+      <c r="R113" s="7" t="s">
         <v>2132</v>
       </c>
-      <c r="O113" s="7" t="s">
+      <c r="S113" s="7" t="s">
         <v>2133</v>
       </c>
-      <c r="P113" s="7" t="s">
+      <c r="T113" s="7" t="s">
         <v>2134</v>
       </c>
-      <c r="Q113" s="7" t="s">
+      <c r="U113" s="7" t="s">
         <v>2135</v>
       </c>
-      <c r="R113" s="7" t="s">
+      <c r="V113" s="7" t="s">
         <v>2136</v>
       </c>
-      <c r="S113" s="7" t="s">
+      <c r="W113" s="7" t="s">
         <v>2137</v>
       </c>
-      <c r="T113" s="7" t="s">
+      <c r="X113" s="7" t="s">
         <v>2138</v>
       </c>
-      <c r="U113" s="7" t="s">
+      <c r="Y113" s="7" t="s">
         <v>2139</v>
       </c>
-      <c r="V113" s="7" t="s">
+      <c r="Z113" s="7" t="s">
+        <v>2137</v>
+      </c>
+      <c r="AA113" s="7" t="s">
         <v>2140</v>
       </c>
-      <c r="W113" s="7" t="s">
-        <v>2141</v>
-      </c>
-      <c r="X113" s="7" t="s">
-        <v>2142</v>
-      </c>
-      <c r="Y113" s="7" t="s">
-        <v>2143</v>
-      </c>
-      <c r="Z113" s="7" t="s">
-        <v>2141</v>
-      </c>
-      <c r="AA113" s="7" t="s">
-        <v>2144</v>
-      </c>
       <c r="AB113" s="7" t="s">
-        <v>2143</v>
+        <v>2139</v>
       </c>
       <c r="AC113" s="7"/>
       <c r="AD113" s="7"/>
       <c r="AE113" s="7" t="s">
-        <v>2145</v>
+        <v>2141</v>
       </c>
       <c r="AF113" s="7">
         <v>1</v>
@@ -20243,13 +20281,13 @@
     </row>
     <row r="114" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A114" s="1" t="s">
-        <v>2337</v>
+        <v>2333</v>
       </c>
       <c r="B114" s="7" t="s">
-        <v>2146</v>
+        <v>2142</v>
       </c>
       <c r="C114" s="7" t="s">
-        <v>2147</v>
+        <v>2143</v>
       </c>
       <c r="D114" s="7" t="s">
         <v>40</v>
@@ -20261,7 +20299,7 @@
         <v>1494</v>
       </c>
       <c r="G114" s="7" t="s">
-        <v>2148</v>
+        <v>2144</v>
       </c>
       <c r="H114" s="7" t="s">
         <v>44</v>
@@ -20278,58 +20316,58 @@
       <c r="L114" s="7">
         <v>7</v>
       </c>
-      <c r="M114" s="7" t="s">
-        <v>2131</v>
+      <c r="M114" s="10" t="s">
+        <v>2360</v>
       </c>
       <c r="N114" s="7" t="s">
+        <v>2145</v>
+      </c>
+      <c r="O114" s="7" t="s">
+        <v>2146</v>
+      </c>
+      <c r="P114" s="7" t="s">
+        <v>2147</v>
+      </c>
+      <c r="Q114" s="7" t="s">
+        <v>2148</v>
+      </c>
+      <c r="R114" s="7" t="s">
+        <v>2143</v>
+      </c>
+      <c r="S114" s="7" t="s">
         <v>2149</v>
       </c>
-      <c r="O114" s="7" t="s">
+      <c r="T114" s="7" t="s">
         <v>2150</v>
       </c>
-      <c r="P114" s="7" t="s">
+      <c r="U114" s="7" t="s">
         <v>2151</v>
       </c>
-      <c r="Q114" s="7" t="s">
+      <c r="V114" s="7" t="s">
         <v>2152</v>
       </c>
-      <c r="R114" s="7" t="s">
-        <v>2147</v>
-      </c>
-      <c r="S114" s="7" t="s">
+      <c r="W114" s="7" t="s">
         <v>2153</v>
       </c>
-      <c r="T114" s="7" t="s">
+      <c r="X114" s="7" t="s">
         <v>2154</v>
       </c>
-      <c r="U114" s="7" t="s">
+      <c r="Y114" s="7" t="s">
+        <v>2139</v>
+      </c>
+      <c r="Z114" s="7" t="s">
         <v>2155</v>
       </c>
-      <c r="V114" s="7" t="s">
+      <c r="AA114" s="7" t="s">
         <v>2156</v>
       </c>
-      <c r="W114" s="7" t="s">
-        <v>2157</v>
-      </c>
-      <c r="X114" s="7" t="s">
-        <v>2158</v>
-      </c>
-      <c r="Y114" s="7" t="s">
-        <v>2143</v>
-      </c>
-      <c r="Z114" s="7" t="s">
-        <v>2159</v>
-      </c>
-      <c r="AA114" s="7" t="s">
-        <v>2160</v>
-      </c>
       <c r="AB114" s="7" t="s">
-        <v>2143</v>
+        <v>2139</v>
       </c>
       <c r="AC114" s="7"/>
       <c r="AD114" s="7"/>
       <c r="AE114" s="7" t="s">
-        <v>2161</v>
+        <v>2157</v>
       </c>
       <c r="AF114" s="7">
         <v>1</v>
@@ -20352,25 +20390,25 @@
     </row>
     <row r="115" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A115" s="1" t="s">
-        <v>2338</v>
+        <v>2334</v>
       </c>
       <c r="B115" s="7" t="s">
-        <v>2162</v>
+        <v>2158</v>
       </c>
       <c r="C115" s="7" t="s">
-        <v>2163</v>
+        <v>2159</v>
       </c>
       <c r="D115" s="7" t="s">
         <v>40</v>
       </c>
       <c r="E115" s="7" t="s">
-        <v>2090</v>
+        <v>2089</v>
       </c>
       <c r="F115" s="7" t="s">
         <v>41</v>
       </c>
       <c r="G115" s="7" t="s">
-        <v>2164</v>
+        <v>2160</v>
       </c>
       <c r="H115" s="7" t="s">
         <v>44</v>
@@ -20387,62 +20425,62 @@
       <c r="L115" s="7">
         <v>5</v>
       </c>
-      <c r="M115" s="7" t="s">
-        <v>2092</v>
+      <c r="M115" s="10" t="s">
+        <v>2348</v>
       </c>
       <c r="N115" s="7" t="s">
+        <v>2161</v>
+      </c>
+      <c r="O115" s="7" t="s">
+        <v>2162</v>
+      </c>
+      <c r="P115" s="7" t="s">
+        <v>2163</v>
+      </c>
+      <c r="Q115" s="7" t="s">
+        <v>2164</v>
+      </c>
+      <c r="R115" s="7" t="s">
         <v>2165</v>
       </c>
-      <c r="O115" s="7" t="s">
+      <c r="S115" s="7" t="s">
         <v>2166</v>
       </c>
-      <c r="P115" s="7" t="s">
+      <c r="T115" s="7" t="s">
         <v>2167</v>
       </c>
-      <c r="Q115" s="7" t="s">
+      <c r="U115" s="7" t="s">
         <v>2168</v>
       </c>
-      <c r="R115" s="7" t="s">
+      <c r="V115" s="7" t="s">
         <v>2169</v>
       </c>
-      <c r="S115" s="7" t="s">
+      <c r="W115" s="7" t="s">
         <v>2170</v>
       </c>
-      <c r="T115" s="7" t="s">
+      <c r="X115" s="7" t="s">
         <v>2171</v>
       </c>
-      <c r="U115" s="7" t="s">
+      <c r="Y115" s="7" t="s">
+        <v>2102</v>
+      </c>
+      <c r="Z115" s="7" t="s">
+        <v>2170</v>
+      </c>
+      <c r="AA115" s="7" t="s">
         <v>2172</v>
       </c>
-      <c r="V115" s="7" t="s">
+      <c r="AB115" s="7" t="s">
+        <v>2102</v>
+      </c>
+      <c r="AC115" s="7" t="s">
         <v>2173</v>
       </c>
-      <c r="W115" s="7" t="s">
+      <c r="AD115" s="7" t="s">
+        <v>2087</v>
+      </c>
+      <c r="AE115" s="7" t="s">
         <v>2174</v>
-      </c>
-      <c r="X115" s="7" t="s">
-        <v>2175</v>
-      </c>
-      <c r="Y115" s="7" t="s">
-        <v>2104</v>
-      </c>
-      <c r="Z115" s="7" t="s">
-        <v>2174</v>
-      </c>
-      <c r="AA115" s="7" t="s">
-        <v>2176</v>
-      </c>
-      <c r="AB115" s="7" t="s">
-        <v>2104</v>
-      </c>
-      <c r="AC115" s="7" t="s">
-        <v>2177</v>
-      </c>
-      <c r="AD115" s="7" t="s">
-        <v>2088</v>
-      </c>
-      <c r="AE115" s="7" t="s">
-        <v>2178</v>
       </c>
       <c r="AF115" s="7">
         <v>0.8</v>
@@ -20454,7 +20492,7 @@
         <v>64</v>
       </c>
       <c r="AI115" s="7" t="s">
-        <v>2179</v>
+        <v>2175</v>
       </c>
       <c r="AJ115" s="7" t="s">
         <v>66</v>
@@ -20465,25 +20503,25 @@
     </row>
     <row r="116" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A116" s="1" t="s">
-        <v>2339</v>
+        <v>2335</v>
       </c>
       <c r="B116" s="7" t="s">
-        <v>2180</v>
+        <v>2176</v>
       </c>
       <c r="C116" s="7" t="s">
-        <v>2181</v>
+        <v>2177</v>
       </c>
       <c r="D116" s="7" t="s">
         <v>40</v>
       </c>
       <c r="E116" s="7" t="s">
-        <v>2090</v>
+        <v>2089</v>
       </c>
       <c r="F116" s="7" t="s">
         <v>93</v>
       </c>
       <c r="G116" s="7" t="s">
-        <v>2182</v>
+        <v>2178</v>
       </c>
       <c r="H116" s="7" t="s">
         <v>44</v>
@@ -20500,62 +20538,62 @@
       <c r="L116" s="7">
         <v>5</v>
       </c>
-      <c r="M116" s="7" t="s">
-        <v>2092</v>
+      <c r="M116" s="10" t="s">
+        <v>2349</v>
       </c>
       <c r="N116" s="7" t="s">
+        <v>2179</v>
+      </c>
+      <c r="O116" s="7" t="s">
+        <v>2180</v>
+      </c>
+      <c r="P116" s="7" t="s">
+        <v>2181</v>
+      </c>
+      <c r="Q116" s="7" t="s">
+        <v>2182</v>
+      </c>
+      <c r="R116" s="7" t="s">
         <v>2183</v>
       </c>
-      <c r="O116" s="7" t="s">
+      <c r="S116" s="7" t="s">
         <v>2184</v>
       </c>
-      <c r="P116" s="7" t="s">
+      <c r="T116" s="7" t="s">
         <v>2185</v>
       </c>
-      <c r="Q116" s="7" t="s">
+      <c r="U116" s="7" t="s">
         <v>2186</v>
       </c>
-      <c r="R116" s="7" t="s">
+      <c r="V116" s="7" t="s">
         <v>2187</v>
       </c>
-      <c r="S116" s="7" t="s">
+      <c r="W116" s="7" t="s">
         <v>2188</v>
       </c>
-      <c r="T116" s="7" t="s">
+      <c r="X116" s="7" t="s">
+        <v>2172</v>
+      </c>
+      <c r="Y116" s="7" t="s">
+        <v>2102</v>
+      </c>
+      <c r="Z116" s="7" t="s">
         <v>2189</v>
       </c>
-      <c r="U116" s="7" t="s">
+      <c r="AA116" s="7" t="s">
         <v>2190</v>
       </c>
-      <c r="V116" s="7" t="s">
+      <c r="AB116" s="7" t="s">
+        <v>2102</v>
+      </c>
+      <c r="AC116" s="7" t="s">
         <v>2191</v>
       </c>
-      <c r="W116" s="7" t="s">
+      <c r="AD116" s="7" t="s">
+        <v>2087</v>
+      </c>
+      <c r="AE116" s="7" t="s">
         <v>2192</v>
-      </c>
-      <c r="X116" s="7" t="s">
-        <v>2176</v>
-      </c>
-      <c r="Y116" s="7" t="s">
-        <v>2104</v>
-      </c>
-      <c r="Z116" s="7" t="s">
-        <v>2193</v>
-      </c>
-      <c r="AA116" s="7" t="s">
-        <v>2194</v>
-      </c>
-      <c r="AB116" s="7" t="s">
-        <v>2104</v>
-      </c>
-      <c r="AC116" s="7" t="s">
-        <v>2195</v>
-      </c>
-      <c r="AD116" s="7" t="s">
-        <v>2088</v>
-      </c>
-      <c r="AE116" s="7" t="s">
-        <v>2196</v>
       </c>
       <c r="AF116" s="7">
         <v>0.8</v>
@@ -20567,7 +20605,7 @@
         <v>64</v>
       </c>
       <c r="AI116" s="7" t="s">
-        <v>2179</v>
+        <v>2175</v>
       </c>
       <c r="AJ116" s="7" t="s">
         <v>66</v>
@@ -20578,25 +20616,25 @@
     </row>
     <row r="117" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A117" s="1" t="s">
-        <v>2340</v>
+        <v>2336</v>
       </c>
       <c r="B117" s="7" t="s">
-        <v>2197</v>
+        <v>2193</v>
       </c>
       <c r="C117" s="7" t="s">
-        <v>2198</v>
+        <v>2194</v>
       </c>
       <c r="D117" s="7" t="s">
         <v>40</v>
       </c>
       <c r="E117" s="7" t="s">
-        <v>2090</v>
+        <v>2089</v>
       </c>
       <c r="F117" s="7" t="s">
         <v>93</v>
       </c>
       <c r="G117" s="7" t="s">
-        <v>2199</v>
+        <v>2195</v>
       </c>
       <c r="H117" s="7" t="s">
         <v>44</v>
@@ -20613,62 +20651,62 @@
       <c r="L117" s="7">
         <v>5</v>
       </c>
-      <c r="M117" s="7" t="s">
-        <v>2092</v>
+      <c r="M117" s="10" t="s">
+        <v>2350</v>
       </c>
       <c r="N117" s="7" t="s">
+        <v>2196</v>
+      </c>
+      <c r="O117" s="7" t="s">
+        <v>2197</v>
+      </c>
+      <c r="P117" s="7" t="s">
+        <v>2198</v>
+      </c>
+      <c r="Q117" s="7" t="s">
+        <v>2199</v>
+      </c>
+      <c r="R117" s="7" t="s">
         <v>2200</v>
       </c>
-      <c r="O117" s="7" t="s">
+      <c r="S117" s="7" t="s">
         <v>2201</v>
       </c>
-      <c r="P117" s="7" t="s">
+      <c r="T117" s="7" t="s">
         <v>2202</v>
       </c>
-      <c r="Q117" s="7" t="s">
+      <c r="U117" s="7" t="s">
         <v>2203</v>
       </c>
-      <c r="R117" s="7" t="s">
+      <c r="V117" s="7" t="s">
         <v>2204</v>
       </c>
-      <c r="S117" s="7" t="s">
+      <c r="W117" s="7" t="s">
         <v>2205</v>
       </c>
-      <c r="T117" s="7" t="s">
+      <c r="X117" s="7" t="s">
+        <v>2166</v>
+      </c>
+      <c r="Y117" s="7" t="s">
+        <v>2102</v>
+      </c>
+      <c r="Z117" s="7" t="s">
         <v>2206</v>
       </c>
-      <c r="U117" s="7" t="s">
+      <c r="AA117" s="7" t="s">
         <v>2207</v>
       </c>
-      <c r="V117" s="7" t="s">
+      <c r="AB117" s="7" t="s">
+        <v>2102</v>
+      </c>
+      <c r="AC117" s="7" t="s">
         <v>2208</v>
       </c>
-      <c r="W117" s="7" t="s">
+      <c r="AD117" s="7" t="s">
+        <v>2087</v>
+      </c>
+      <c r="AE117" s="7" t="s">
         <v>2209</v>
-      </c>
-      <c r="X117" s="7" t="s">
-        <v>2170</v>
-      </c>
-      <c r="Y117" s="7" t="s">
-        <v>2104</v>
-      </c>
-      <c r="Z117" s="7" t="s">
-        <v>2210</v>
-      </c>
-      <c r="AA117" s="7" t="s">
-        <v>2211</v>
-      </c>
-      <c r="AB117" s="7" t="s">
-        <v>2104</v>
-      </c>
-      <c r="AC117" s="7" t="s">
-        <v>2212</v>
-      </c>
-      <c r="AD117" s="7" t="s">
-        <v>2088</v>
-      </c>
-      <c r="AE117" s="7" t="s">
-        <v>2213</v>
       </c>
       <c r="AF117" s="7">
         <v>0.8</v>
@@ -20680,7 +20718,7 @@
         <v>64</v>
       </c>
       <c r="AI117" s="7" t="s">
-        <v>2179</v>
+        <v>2175</v>
       </c>
       <c r="AJ117" s="7" t="s">
         <v>66</v>
@@ -20691,25 +20729,25 @@
     </row>
     <row r="118" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A118" s="1" t="s">
-        <v>2341</v>
+        <v>2337</v>
       </c>
       <c r="B118" s="7" t="s">
-        <v>2214</v>
+        <v>2210</v>
       </c>
       <c r="C118" s="7" t="s">
-        <v>2215</v>
+        <v>2211</v>
       </c>
       <c r="D118" s="7" t="s">
         <v>40</v>
       </c>
       <c r="E118" s="7" t="s">
-        <v>2090</v>
+        <v>2089</v>
       </c>
       <c r="F118" s="7" t="s">
         <v>93</v>
       </c>
       <c r="G118" s="7" t="s">
-        <v>2216</v>
+        <v>2212</v>
       </c>
       <c r="H118" s="7" t="s">
         <v>44</v>
@@ -20726,62 +20764,62 @@
       <c r="L118" s="7">
         <v>5</v>
       </c>
-      <c r="M118" s="7" t="s">
-        <v>2092</v>
+      <c r="M118" s="10" t="s">
+        <v>2351</v>
       </c>
       <c r="N118" s="7" t="s">
+        <v>2213</v>
+      </c>
+      <c r="O118" s="7" t="s">
+        <v>2214</v>
+      </c>
+      <c r="P118" s="7" t="s">
+        <v>2215</v>
+      </c>
+      <c r="Q118" s="7" t="s">
+        <v>2216</v>
+      </c>
+      <c r="R118" s="7" t="s">
         <v>2217</v>
       </c>
-      <c r="O118" s="7" t="s">
+      <c r="S118" s="7" t="s">
         <v>2218</v>
       </c>
-      <c r="P118" s="7" t="s">
+      <c r="T118" s="7" t="s">
         <v>2219</v>
       </c>
-      <c r="Q118" s="7" t="s">
+      <c r="U118" s="7" t="s">
         <v>2220</v>
       </c>
-      <c r="R118" s="7" t="s">
+      <c r="V118" s="7" t="s">
         <v>2221</v>
       </c>
-      <c r="S118" s="7" t="s">
+      <c r="W118" s="7" t="s">
         <v>2222</v>
       </c>
-      <c r="T118" s="7" t="s">
+      <c r="X118" s="7" t="s">
+        <v>2166</v>
+      </c>
+      <c r="Y118" s="7" t="s">
+        <v>2102</v>
+      </c>
+      <c r="Z118" s="7" t="s">
         <v>2223</v>
       </c>
-      <c r="U118" s="7" t="s">
+      <c r="AA118" s="7" t="s">
         <v>2224</v>
       </c>
-      <c r="V118" s="7" t="s">
+      <c r="AB118" s="7" t="s">
+        <v>2102</v>
+      </c>
+      <c r="AC118" s="7" t="s">
+        <v>2191</v>
+      </c>
+      <c r="AD118" s="7" t="s">
+        <v>2193</v>
+      </c>
+      <c r="AE118" s="7" t="s">
         <v>2225</v>
-      </c>
-      <c r="W118" s="7" t="s">
-        <v>2226</v>
-      </c>
-      <c r="X118" s="7" t="s">
-        <v>2170</v>
-      </c>
-      <c r="Y118" s="7" t="s">
-        <v>2104</v>
-      </c>
-      <c r="Z118" s="7" t="s">
-        <v>2227</v>
-      </c>
-      <c r="AA118" s="7" t="s">
-        <v>2228</v>
-      </c>
-      <c r="AB118" s="7" t="s">
-        <v>2104</v>
-      </c>
-      <c r="AC118" s="7" t="s">
-        <v>2195</v>
-      </c>
-      <c r="AD118" s="7" t="s">
-        <v>2197</v>
-      </c>
-      <c r="AE118" s="7" t="s">
-        <v>2229</v>
       </c>
       <c r="AF118" s="7">
         <v>0.8</v>
@@ -20793,7 +20831,7 @@
         <v>64</v>
       </c>
       <c r="AI118" s="7" t="s">
-        <v>2179</v>
+        <v>2175</v>
       </c>
       <c r="AJ118" s="7" t="s">
         <v>66</v>
@@ -20804,25 +20842,25 @@
     </row>
     <row r="119" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A119" s="1" t="s">
-        <v>2342</v>
+        <v>2338</v>
       </c>
       <c r="B119" s="7" t="s">
-        <v>2230</v>
+        <v>2226</v>
       </c>
       <c r="C119" s="7" t="s">
-        <v>2231</v>
+        <v>2227</v>
       </c>
       <c r="D119" s="7" t="s">
         <v>40</v>
       </c>
       <c r="E119" s="7" t="s">
-        <v>2090</v>
+        <v>2089</v>
       </c>
       <c r="F119" s="7" t="s">
         <v>93</v>
       </c>
       <c r="G119" s="7" t="s">
-        <v>2232</v>
+        <v>2228</v>
       </c>
       <c r="H119" s="7" t="s">
         <v>44</v>
@@ -20839,62 +20877,62 @@
       <c r="L119" s="7">
         <v>5</v>
       </c>
-      <c r="M119" s="7" t="s">
-        <v>2092</v>
+      <c r="M119" s="10" t="s">
+        <v>2352</v>
       </c>
       <c r="N119" s="7" t="s">
+        <v>2229</v>
+      </c>
+      <c r="O119" s="7" t="s">
+        <v>2230</v>
+      </c>
+      <c r="P119" s="7" t="s">
+        <v>2231</v>
+      </c>
+      <c r="Q119" s="7" t="s">
+        <v>2232</v>
+      </c>
+      <c r="R119" s="7" t="s">
         <v>2233</v>
       </c>
-      <c r="O119" s="7" t="s">
+      <c r="S119" s="7" t="s">
         <v>2234</v>
       </c>
-      <c r="P119" s="7" t="s">
+      <c r="T119" s="7" t="s">
         <v>2235</v>
       </c>
-      <c r="Q119" s="7" t="s">
+      <c r="U119" s="7" t="s">
         <v>2236</v>
       </c>
-      <c r="R119" s="7" t="s">
+      <c r="V119" s="7" t="s">
         <v>2237</v>
       </c>
-      <c r="S119" s="7" t="s">
+      <c r="W119" s="7" t="s">
+        <v>2233</v>
+      </c>
+      <c r="X119" s="7" t="s">
+        <v>2166</v>
+      </c>
+      <c r="Y119" s="7" t="s">
+        <v>2102</v>
+      </c>
+      <c r="Z119" s="7" t="s">
         <v>2238</v>
       </c>
-      <c r="T119" s="7" t="s">
+      <c r="AA119" s="7" t="s">
+        <v>2190</v>
+      </c>
+      <c r="AB119" s="7" t="s">
+        <v>2102</v>
+      </c>
+      <c r="AC119" s="7" t="s">
+        <v>2173</v>
+      </c>
+      <c r="AD119" s="7" t="s">
+        <v>2106</v>
+      </c>
+      <c r="AE119" s="7" t="s">
         <v>2239</v>
-      </c>
-      <c r="U119" s="7" t="s">
-        <v>2240</v>
-      </c>
-      <c r="V119" s="7" t="s">
-        <v>2241</v>
-      </c>
-      <c r="W119" s="7" t="s">
-        <v>2237</v>
-      </c>
-      <c r="X119" s="7" t="s">
-        <v>2170</v>
-      </c>
-      <c r="Y119" s="7" t="s">
-        <v>2104</v>
-      </c>
-      <c r="Z119" s="7" t="s">
-        <v>2242</v>
-      </c>
-      <c r="AA119" s="7" t="s">
-        <v>2194</v>
-      </c>
-      <c r="AB119" s="7" t="s">
-        <v>2104</v>
-      </c>
-      <c r="AC119" s="7" t="s">
-        <v>2177</v>
-      </c>
-      <c r="AD119" s="7" t="s">
-        <v>2108</v>
-      </c>
-      <c r="AE119" s="7" t="s">
-        <v>2243</v>
       </c>
       <c r="AF119" s="7">
         <v>0.8</v>
@@ -20906,7 +20944,7 @@
         <v>64</v>
       </c>
       <c r="AI119" s="7" t="s">
-        <v>2179</v>
+        <v>2175</v>
       </c>
       <c r="AJ119" s="7" t="s">
         <v>66</v>
@@ -20917,25 +20955,25 @@
     </row>
     <row r="120" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A120" s="1" t="s">
-        <v>2343</v>
+        <v>2339</v>
       </c>
       <c r="B120" s="7" t="s">
-        <v>2244</v>
+        <v>2240</v>
       </c>
       <c r="C120" s="7" t="s">
-        <v>2245</v>
+        <v>2241</v>
       </c>
       <c r="D120" s="7" t="s">
         <v>40</v>
       </c>
       <c r="E120" s="7" t="s">
-        <v>2090</v>
+        <v>2089</v>
       </c>
       <c r="F120" s="7" t="s">
         <v>93</v>
       </c>
       <c r="G120" s="7" t="s">
-        <v>2246</v>
+        <v>2242</v>
       </c>
       <c r="H120" s="7" t="s">
         <v>44</v>
@@ -20952,62 +20990,62 @@
       <c r="L120" s="7">
         <v>5</v>
       </c>
-      <c r="M120" s="7" t="s">
-        <v>2092</v>
+      <c r="M120" s="10" t="s">
+        <v>2353</v>
       </c>
       <c r="N120" s="7" t="s">
+        <v>2243</v>
+      </c>
+      <c r="O120" s="7" t="s">
+        <v>2244</v>
+      </c>
+      <c r="P120" s="7" t="s">
+        <v>2245</v>
+      </c>
+      <c r="Q120" s="7" t="s">
+        <v>2246</v>
+      </c>
+      <c r="R120" s="7" t="s">
         <v>2247</v>
       </c>
-      <c r="O120" s="7" t="s">
+      <c r="S120" s="7" t="s">
         <v>2248</v>
       </c>
-      <c r="P120" s="7" t="s">
+      <c r="T120" s="7" t="s">
         <v>2249</v>
       </c>
-      <c r="Q120" s="7" t="s">
+      <c r="U120" s="7" t="s">
         <v>2250</v>
       </c>
-      <c r="R120" s="7" t="s">
+      <c r="V120" s="7" t="s">
         <v>2251</v>
       </c>
-      <c r="S120" s="7" t="s">
+      <c r="W120" s="7" t="s">
+        <v>2247</v>
+      </c>
+      <c r="X120" s="7" t="s">
+        <v>2172</v>
+      </c>
+      <c r="Y120" s="7" t="s">
+        <v>2102</v>
+      </c>
+      <c r="Z120" s="7" t="s">
         <v>2252</v>
       </c>
-      <c r="T120" s="7" t="s">
+      <c r="AA120" s="7" t="s">
+        <v>2190</v>
+      </c>
+      <c r="AB120" s="7" t="s">
+        <v>2102</v>
+      </c>
+      <c r="AC120" s="7" t="s">
+        <v>2208</v>
+      </c>
+      <c r="AD120" s="7" t="s">
+        <v>2106</v>
+      </c>
+      <c r="AE120" s="7" t="s">
         <v>2253</v>
-      </c>
-      <c r="U120" s="7" t="s">
-        <v>2254</v>
-      </c>
-      <c r="V120" s="7" t="s">
-        <v>2255</v>
-      </c>
-      <c r="W120" s="7" t="s">
-        <v>2251</v>
-      </c>
-      <c r="X120" s="7" t="s">
-        <v>2176</v>
-      </c>
-      <c r="Y120" s="7" t="s">
-        <v>2104</v>
-      </c>
-      <c r="Z120" s="7" t="s">
-        <v>2256</v>
-      </c>
-      <c r="AA120" s="7" t="s">
-        <v>2194</v>
-      </c>
-      <c r="AB120" s="7" t="s">
-        <v>2104</v>
-      </c>
-      <c r="AC120" s="7" t="s">
-        <v>2212</v>
-      </c>
-      <c r="AD120" s="7" t="s">
-        <v>2108</v>
-      </c>
-      <c r="AE120" s="7" t="s">
-        <v>2257</v>
       </c>
       <c r="AF120" s="7">
         <v>0.8</v>
@@ -21019,7 +21057,7 @@
         <v>64</v>
       </c>
       <c r="AI120" s="7" t="s">
-        <v>2179</v>
+        <v>2175</v>
       </c>
       <c r="AJ120" s="7" t="s">
         <v>66</v>
@@ -21030,25 +21068,25 @@
     </row>
     <row r="121" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A121" s="1" t="s">
-        <v>2344</v>
+        <v>2340</v>
       </c>
       <c r="B121" s="7" t="s">
-        <v>2258</v>
+        <v>2254</v>
       </c>
       <c r="C121" s="7" t="s">
-        <v>2259</v>
+        <v>2255</v>
       </c>
       <c r="D121" s="7" t="s">
         <v>40</v>
       </c>
       <c r="E121" s="7" t="s">
-        <v>2090</v>
+        <v>2089</v>
       </c>
       <c r="F121" s="7" t="s">
         <v>93</v>
       </c>
       <c r="G121" s="7" t="s">
-        <v>2260</v>
+        <v>2256</v>
       </c>
       <c r="H121" s="7" t="s">
         <v>44</v>
@@ -21065,62 +21103,62 @@
       <c r="L121" s="7">
         <v>5</v>
       </c>
-      <c r="M121" s="7" t="s">
-        <v>2092</v>
+      <c r="M121" s="10" t="s">
+        <v>2354</v>
       </c>
       <c r="N121" s="7" t="s">
+        <v>2257</v>
+      </c>
+      <c r="O121" s="7" t="s">
+        <v>2258</v>
+      </c>
+      <c r="P121" s="7" t="s">
+        <v>2166</v>
+      </c>
+      <c r="Q121" s="7" t="s">
+        <v>2259</v>
+      </c>
+      <c r="R121" s="7" t="s">
+        <v>2260</v>
+      </c>
+      <c r="S121" s="7" t="s">
         <v>2261</v>
       </c>
-      <c r="O121" s="7" t="s">
+      <c r="T121" s="7" t="s">
         <v>2262</v>
       </c>
-      <c r="P121" s="7" t="s">
-        <v>2170</v>
-      </c>
-      <c r="Q121" s="7" t="s">
+      <c r="U121" s="7" t="s">
         <v>2263</v>
       </c>
-      <c r="R121" s="7" t="s">
+      <c r="V121" s="7" t="s">
         <v>2264</v>
       </c>
-      <c r="S121" s="7" t="s">
+      <c r="W121" s="7" t="s">
         <v>2265</v>
       </c>
-      <c r="T121" s="7" t="s">
+      <c r="X121" s="7" t="s">
+        <v>2166</v>
+      </c>
+      <c r="Y121" s="7" t="s">
+        <v>2102</v>
+      </c>
+      <c r="Z121" s="7" t="s">
         <v>2266</v>
       </c>
-      <c r="U121" s="7" t="s">
+      <c r="AA121" s="7" t="s">
+        <v>2218</v>
+      </c>
+      <c r="AB121" s="7" t="s">
+        <v>2102</v>
+      </c>
+      <c r="AC121" s="7" t="s">
+        <v>2191</v>
+      </c>
+      <c r="AD121" s="7" t="s">
+        <v>2226</v>
+      </c>
+      <c r="AE121" s="7" t="s">
         <v>2267</v>
-      </c>
-      <c r="V121" s="7" t="s">
-        <v>2268</v>
-      </c>
-      <c r="W121" s="7" t="s">
-        <v>2269</v>
-      </c>
-      <c r="X121" s="7" t="s">
-        <v>2170</v>
-      </c>
-      <c r="Y121" s="7" t="s">
-        <v>2104</v>
-      </c>
-      <c r="Z121" s="7" t="s">
-        <v>2270</v>
-      </c>
-      <c r="AA121" s="7" t="s">
-        <v>2222</v>
-      </c>
-      <c r="AB121" s="7" t="s">
-        <v>2104</v>
-      </c>
-      <c r="AC121" s="7" t="s">
-        <v>2195</v>
-      </c>
-      <c r="AD121" s="7" t="s">
-        <v>2230</v>
-      </c>
-      <c r="AE121" s="7" t="s">
-        <v>2271</v>
       </c>
       <c r="AF121" s="7">
         <v>0.8</v>
@@ -21132,7 +21170,7 @@
         <v>64</v>
       </c>
       <c r="AI121" s="7" t="s">
-        <v>2179</v>
+        <v>2175</v>
       </c>
       <c r="AJ121" s="7" t="s">
         <v>66</v>
@@ -21143,25 +21181,25 @@
     </row>
     <row r="122" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A122" s="1" t="s">
-        <v>2345</v>
+        <v>2341</v>
       </c>
       <c r="B122" s="7" t="s">
-        <v>2272</v>
+        <v>2268</v>
       </c>
       <c r="C122" s="7" t="s">
-        <v>2273</v>
+        <v>2269</v>
       </c>
       <c r="D122" s="7" t="s">
         <v>40</v>
       </c>
       <c r="E122" s="7" t="s">
-        <v>2090</v>
+        <v>2089</v>
       </c>
       <c r="F122" s="7" t="s">
         <v>41</v>
       </c>
       <c r="G122" s="7" t="s">
-        <v>2274</v>
+        <v>2270</v>
       </c>
       <c r="H122" s="7" t="s">
         <v>44</v>
@@ -21178,62 +21216,62 @@
       <c r="L122" s="7">
         <v>5</v>
       </c>
-      <c r="M122" s="7" t="s">
-        <v>2092</v>
+      <c r="M122" s="10" t="s">
+        <v>2355</v>
       </c>
       <c r="N122" s="7" t="s">
+        <v>2271</v>
+      </c>
+      <c r="O122" s="7" t="s">
+        <v>2272</v>
+      </c>
+      <c r="P122" s="7" t="s">
+        <v>2273</v>
+      </c>
+      <c r="Q122" s="7" t="s">
+        <v>2274</v>
+      </c>
+      <c r="R122" s="7" t="s">
         <v>2275</v>
       </c>
-      <c r="O122" s="7" t="s">
+      <c r="S122" s="7" t="s">
+        <v>2248</v>
+      </c>
+      <c r="T122" s="7" t="s">
         <v>2276</v>
       </c>
-      <c r="P122" s="7" t="s">
+      <c r="U122" s="7" t="s">
         <v>2277</v>
       </c>
-      <c r="Q122" s="7" t="s">
+      <c r="V122" s="7" t="s">
         <v>2278</v>
       </c>
-      <c r="R122" s="7" t="s">
+      <c r="W122" s="7" t="s">
+        <v>2275</v>
+      </c>
+      <c r="X122" s="7" t="s">
         <v>2279</v>
       </c>
-      <c r="S122" s="7" t="s">
-        <v>2252</v>
-      </c>
-      <c r="T122" s="7" t="s">
+      <c r="Y122" s="7" t="s">
+        <v>2102</v>
+      </c>
+      <c r="Z122" s="7" t="s">
         <v>2280</v>
       </c>
-      <c r="U122" s="7" t="s">
+      <c r="AA122" s="7" t="s">
+        <v>2190</v>
+      </c>
+      <c r="AB122" s="7" t="s">
+        <v>2102</v>
+      </c>
+      <c r="AC122" s="7" t="s">
+        <v>2173</v>
+      </c>
+      <c r="AD122" s="7" t="s">
+        <v>2106</v>
+      </c>
+      <c r="AE122" s="7" t="s">
         <v>2281</v>
-      </c>
-      <c r="V122" s="7" t="s">
-        <v>2282</v>
-      </c>
-      <c r="W122" s="7" t="s">
-        <v>2279</v>
-      </c>
-      <c r="X122" s="7" t="s">
-        <v>2283</v>
-      </c>
-      <c r="Y122" s="7" t="s">
-        <v>2104</v>
-      </c>
-      <c r="Z122" s="7" t="s">
-        <v>2284</v>
-      </c>
-      <c r="AA122" s="7" t="s">
-        <v>2194</v>
-      </c>
-      <c r="AB122" s="7" t="s">
-        <v>2104</v>
-      </c>
-      <c r="AC122" s="7" t="s">
-        <v>2177</v>
-      </c>
-      <c r="AD122" s="7" t="s">
-        <v>2108</v>
-      </c>
-      <c r="AE122" s="7" t="s">
-        <v>2285</v>
       </c>
       <c r="AF122" s="7">
         <v>0.8</v>
@@ -21245,7 +21283,7 @@
         <v>64</v>
       </c>
       <c r="AI122" s="7" t="s">
-        <v>2179</v>
+        <v>2175</v>
       </c>
       <c r="AJ122" s="7" t="s">
         <v>66</v>
@@ -21256,13 +21294,13 @@
     </row>
     <row r="123" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A123" s="1" t="s">
-        <v>2346</v>
+        <v>2342</v>
       </c>
       <c r="B123" s="7" t="s">
-        <v>2286</v>
+        <v>2282</v>
       </c>
       <c r="C123" s="7" t="s">
-        <v>2287</v>
+        <v>2283</v>
       </c>
       <c r="D123" s="7" t="s">
         <v>40</v>
@@ -21274,7 +21312,7 @@
         <v>1494</v>
       </c>
       <c r="G123" s="7" t="s">
-        <v>2288</v>
+        <v>2284</v>
       </c>
       <c r="H123" s="7" t="s">
         <v>44</v>
@@ -21291,58 +21329,58 @@
       <c r="L123" s="7">
         <v>6</v>
       </c>
-      <c r="M123" s="7" t="s">
-        <v>2131</v>
+      <c r="M123" s="10" t="s">
+        <v>2356</v>
       </c>
       <c r="N123" s="7" t="s">
+        <v>2285</v>
+      </c>
+      <c r="O123" s="7" t="s">
+        <v>2286</v>
+      </c>
+      <c r="P123" s="7" t="s">
+        <v>2287</v>
+      </c>
+      <c r="Q123" s="7" t="s">
+        <v>2288</v>
+      </c>
+      <c r="R123" s="7" t="s">
         <v>2289</v>
       </c>
-      <c r="O123" s="7" t="s">
+      <c r="S123" s="7" t="s">
         <v>2290</v>
       </c>
-      <c r="P123" s="7" t="s">
+      <c r="T123" s="7" t="s">
         <v>2291</v>
       </c>
-      <c r="Q123" s="7" t="s">
+      <c r="U123" s="7" t="s">
         <v>2292</v>
       </c>
-      <c r="R123" s="7" t="s">
+      <c r="V123" s="7" t="s">
         <v>2293</v>
       </c>
-      <c r="S123" s="7" t="s">
+      <c r="W123" s="7" t="s">
+        <v>2289</v>
+      </c>
+      <c r="X123" s="7" t="s">
+        <v>2156</v>
+      </c>
+      <c r="Y123" s="7" t="s">
+        <v>2139</v>
+      </c>
+      <c r="Z123" s="7" t="s">
         <v>2294</v>
       </c>
-      <c r="T123" s="7" t="s">
+      <c r="AA123" s="7" t="s">
         <v>2295</v>
       </c>
-      <c r="U123" s="7" t="s">
-        <v>2296</v>
-      </c>
-      <c r="V123" s="7" t="s">
-        <v>2297</v>
-      </c>
-      <c r="W123" s="7" t="s">
-        <v>2293</v>
-      </c>
-      <c r="X123" s="7" t="s">
-        <v>2160</v>
-      </c>
-      <c r="Y123" s="7" t="s">
-        <v>2143</v>
-      </c>
-      <c r="Z123" s="7" t="s">
-        <v>2298</v>
-      </c>
-      <c r="AA123" s="7" t="s">
-        <v>2299</v>
-      </c>
       <c r="AB123" s="7" t="s">
-        <v>2143</v>
+        <v>2139</v>
       </c>
       <c r="AC123" s="7"/>
       <c r="AD123" s="7"/>
       <c r="AE123" s="7" t="s">
-        <v>2300</v>
+        <v>2296</v>
       </c>
       <c r="AF123" s="7">
         <v>1</v>
@@ -21365,13 +21403,13 @@
     </row>
     <row r="124" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A124" s="1" t="s">
-        <v>2347</v>
+        <v>2343</v>
       </c>
       <c r="B124" s="7" t="s">
-        <v>2301</v>
+        <v>2297</v>
       </c>
       <c r="C124" s="7" t="s">
-        <v>2302</v>
+        <v>2298</v>
       </c>
       <c r="D124" s="7" t="s">
         <v>40</v>
@@ -21383,7 +21421,7 @@
         <v>1494</v>
       </c>
       <c r="G124" s="7" t="s">
-        <v>2303</v>
+        <v>2299</v>
       </c>
       <c r="H124" s="7" t="s">
         <v>44</v>
@@ -21400,58 +21438,58 @@
       <c r="L124" s="7">
         <v>6</v>
       </c>
-      <c r="M124" s="7" t="s">
-        <v>2131</v>
+      <c r="M124" s="10" t="s">
+        <v>2358</v>
       </c>
       <c r="N124" s="7" t="s">
+        <v>2300</v>
+      </c>
+      <c r="O124" s="7" t="s">
+        <v>2301</v>
+      </c>
+      <c r="P124" s="7" t="s">
+        <v>2302</v>
+      </c>
+      <c r="Q124" s="7" t="s">
+        <v>2303</v>
+      </c>
+      <c r="R124" s="7" t="s">
         <v>2304</v>
       </c>
-      <c r="O124" s="7" t="s">
+      <c r="S124" s="7" t="s">
         <v>2305</v>
       </c>
-      <c r="P124" s="7" t="s">
+      <c r="T124" s="7" t="s">
         <v>2306</v>
       </c>
-      <c r="Q124" s="7" t="s">
+      <c r="U124" s="7" t="s">
         <v>2307</v>
       </c>
-      <c r="R124" s="7" t="s">
+      <c r="V124" s="7" t="s">
         <v>2308</v>
       </c>
-      <c r="S124" s="7" t="s">
-        <v>2309</v>
-      </c>
-      <c r="T124" s="7" t="s">
-        <v>2310</v>
-      </c>
-      <c r="U124" s="7" t="s">
-        <v>2311</v>
-      </c>
-      <c r="V124" s="7" t="s">
-        <v>2312</v>
-      </c>
       <c r="W124" s="7" t="s">
-        <v>2308</v>
+        <v>2304</v>
       </c>
       <c r="X124" s="7" t="s">
         <v>258</v>
       </c>
       <c r="Y124" s="7" t="s">
-        <v>2143</v>
+        <v>2139</v>
       </c>
       <c r="Z124" s="7" t="s">
-        <v>2313</v>
+        <v>2309</v>
       </c>
       <c r="AA124" s="7" t="s">
-        <v>2314</v>
+        <v>2310</v>
       </c>
       <c r="AB124" s="7" t="s">
-        <v>2143</v>
+        <v>2139</v>
       </c>
       <c r="AC124" s="7"/>
       <c r="AD124" s="7"/>
       <c r="AE124" s="7" t="s">
-        <v>2315</v>
+        <v>2311</v>
       </c>
       <c r="AF124" s="7">
         <v>1</v>
@@ -21474,13 +21512,13 @@
     </row>
     <row r="125" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A125" s="1" t="s">
-        <v>2348</v>
+        <v>2344</v>
       </c>
       <c r="B125" s="7" t="s">
-        <v>2316</v>
+        <v>2312</v>
       </c>
       <c r="C125" s="7" t="s">
-        <v>2317</v>
+        <v>2313</v>
       </c>
       <c r="D125" s="7" t="s">
         <v>40</v>
@@ -21489,10 +21527,10 @@
         <v>70</v>
       </c>
       <c r="F125" s="7" t="s">
-        <v>2318</v>
+        <v>2314</v>
       </c>
       <c r="G125" s="7" t="s">
-        <v>2319</v>
+        <v>2315</v>
       </c>
       <c r="H125" s="7" t="s">
         <v>44</v>
@@ -21509,58 +21547,58 @@
       <c r="L125" s="7">
         <v>6</v>
       </c>
-      <c r="M125" s="7" t="s">
-        <v>2131</v>
+      <c r="M125" s="10" t="s">
+        <v>2357</v>
       </c>
       <c r="N125" s="7" t="s">
+        <v>2316</v>
+      </c>
+      <c r="O125" s="7" t="s">
+        <v>2317</v>
+      </c>
+      <c r="P125" s="7" t="s">
+        <v>2318</v>
+      </c>
+      <c r="Q125" s="7" t="s">
+        <v>2319</v>
+      </c>
+      <c r="R125" s="7" t="s">
         <v>2320</v>
       </c>
-      <c r="O125" s="7" t="s">
+      <c r="S125" s="7" t="s">
         <v>2321</v>
       </c>
-      <c r="P125" s="7" t="s">
+      <c r="T125" s="7" t="s">
         <v>2322</v>
       </c>
-      <c r="Q125" s="7" t="s">
+      <c r="U125" s="7" t="s">
         <v>2323</v>
       </c>
-      <c r="R125" s="7" t="s">
+      <c r="V125" s="7" t="s">
         <v>2324</v>
       </c>
-      <c r="S125" s="7" t="s">
+      <c r="W125" s="7" t="s">
         <v>2325</v>
       </c>
-      <c r="T125" s="7" t="s">
+      <c r="X125" s="7" t="s">
         <v>2326</v>
       </c>
-      <c r="U125" s="7" t="s">
+      <c r="Y125" s="7" t="s">
+        <v>2139</v>
+      </c>
+      <c r="Z125" s="7" t="s">
         <v>2327</v>
       </c>
-      <c r="V125" s="7" t="s">
+      <c r="AA125" s="7" t="s">
         <v>2328</v>
       </c>
-      <c r="W125" s="7" t="s">
-        <v>2329</v>
-      </c>
-      <c r="X125" s="7" t="s">
-        <v>2330</v>
-      </c>
-      <c r="Y125" s="7" t="s">
-        <v>2143</v>
-      </c>
-      <c r="Z125" s="7" t="s">
-        <v>2331</v>
-      </c>
-      <c r="AA125" s="7" t="s">
-        <v>2332</v>
-      </c>
       <c r="AB125" s="7" t="s">
-        <v>2143</v>
+        <v>2139</v>
       </c>
       <c r="AC125" s="7"/>
       <c r="AD125" s="7"/>
       <c r="AE125" s="7" t="s">
-        <v>2333</v>
+        <v>2329</v>
       </c>
       <c r="AF125" s="7">
         <v>1</v>
@@ -21579,26 +21617,18 @@
       </c>
       <c r="AK125" s="1">
         <v>124</v>
-      </c>
-    </row>
-    <row r="126" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="I126" s="8">
-        <v>46234</v>
-      </c>
-      <c r="J126" s="8">
-        <v>46234</v>
-      </c>
-    </row>
-    <row r="127" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="I127" s="8">
-        <v>46234</v>
-      </c>
-      <c r="J127" s="8">
-        <v>46234</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="AB109:AD109"/>
+    <mergeCell ref="AB110:AD110"/>
+    <mergeCell ref="AB103:AD103"/>
+    <mergeCell ref="AB104:AD104"/>
+    <mergeCell ref="AB105:AD105"/>
+    <mergeCell ref="AB106:AD106"/>
+    <mergeCell ref="AB107:AD107"/>
+    <mergeCell ref="AB108:AD108"/>
     <mergeCell ref="AB102:AD102"/>
     <mergeCell ref="AB91:AD91"/>
     <mergeCell ref="AB92:AD92"/>
@@ -21611,14 +21641,6 @@
     <mergeCell ref="AB99:AD99"/>
     <mergeCell ref="AB100:AD100"/>
     <mergeCell ref="AB101:AD101"/>
-    <mergeCell ref="AB109:AD109"/>
-    <mergeCell ref="AB110:AD110"/>
-    <mergeCell ref="AB103:AD103"/>
-    <mergeCell ref="AB104:AD104"/>
-    <mergeCell ref="AB105:AD105"/>
-    <mergeCell ref="AB106:AD106"/>
-    <mergeCell ref="AB107:AD107"/>
-    <mergeCell ref="AB108:AD108"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <hyperlinks>
@@ -22269,12 +22291,11 @@
     <hyperlink ref="Y109" r:id="rId645" xr:uid="{47E1B515-1D33-40F9-8DDA-919F806A35B0}"/>
     <hyperlink ref="AB109" r:id="rId646" xr:uid="{0E5204C4-7A97-4BF6-9197-82E2D54BEFD5}"/>
     <hyperlink ref="AE109" r:id="rId647" xr:uid="{9AF8953E-B574-41CD-A489-151663024CC2}"/>
-    <hyperlink ref="M110" r:id="rId648" xr:uid="{D3565B45-45DD-48E3-9BBA-A1DC1083F99A}"/>
-    <hyperlink ref="Q110" r:id="rId649" xr:uid="{B98A8E67-6651-4244-96BD-E71F41D0D38C}"/>
-    <hyperlink ref="V110" r:id="rId650" xr:uid="{D5F8F0D8-4ED7-454E-9B44-CDD6E2E88890}"/>
-    <hyperlink ref="Y110" r:id="rId651" xr:uid="{D4F9381A-0A91-4DC9-9EE0-53B5D5C3815C}"/>
-    <hyperlink ref="AB110" r:id="rId652" xr:uid="{9F9932CD-05A0-4240-8745-A3A4A7F3881C}"/>
-    <hyperlink ref="AE110" r:id="rId653" xr:uid="{6D88C61F-5BF3-489A-8ADB-5F7021459E0C}"/>
+    <hyperlink ref="Q110" r:id="rId648" xr:uid="{B98A8E67-6651-4244-96BD-E71F41D0D38C}"/>
+    <hyperlink ref="V110" r:id="rId649" xr:uid="{D5F8F0D8-4ED7-454E-9B44-CDD6E2E88890}"/>
+    <hyperlink ref="Y110" r:id="rId650" xr:uid="{D4F9381A-0A91-4DC9-9EE0-53B5D5C3815C}"/>
+    <hyperlink ref="AB110" r:id="rId651" xr:uid="{9F9932CD-05A0-4240-8745-A3A4A7F3881C}"/>
+    <hyperlink ref="AE110" r:id="rId652" xr:uid="{6D88C61F-5BF3-489A-8ADB-5F7021459E0C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/src/data/blogs.xlsx
+++ b/src/data/blogs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Gala\Documents\code\jk3\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90DAD24A-1B46-4393-BAE9-C1B9B129FD72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12F59D8C-A7F7-4520-8946-96EA901BE860}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="84" yWindow="120" windowWidth="11808" windowHeight="11076" xr2:uid="{6540F3E8-6E2B-46EF-8B33-43A96A14636B}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6540F3E8-6E2B-46EF-8B33-43A96A14636B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3780" uniqueCount="2361">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4135" uniqueCount="2598">
   <si>
     <t>BlogID</t>
   </si>
@@ -7314,6 +7314,717 @@
   </si>
   <si>
     <t>https://images.unsplash.com/photo-1680355065203-43ad84bb6e69?q=80&amp;w=965&amp;auto=format&amp;fit=crop&amp;ixlib=rb-4.1.0&amp;ixid=M3wxMjA3fDB8MHxwaG90by1wYWdlfHx8fGVufDB8fHx8fA%3D%3D</t>
+  </si>
+  <si>
+    <t>itr-filing-deadline-ay-2026-27</t>
+  </si>
+  <si>
+    <t>ITR Filing Deadline AY 2026-27: Will Government Extend the Due Date?</t>
+  </si>
+  <si>
+    <t>Income Tax</t>
+  </si>
+  <si>
+    <t>ITR Filing</t>
+  </si>
+  <si>
+    <t>itr deadline,itr extension,income tax return</t>
+  </si>
+  <si>
+    <t>https://images.unsplash.com/photo-1554224155-6726b3ff858f?w=1200</t>
+  </si>
+  <si>
+    <t>itr-deadline.webp</t>
+  </si>
+  <si>
+    <t>Income tax filing online</t>
+  </si>
+  <si>
+    <t>Latest update on ITR filing deadline, who should file before July 31 and why experts don't expect another extension.</t>
+  </si>
+  <si>
+    <t>itr-filing-deadline-ay-2026-27.md</t>
+  </si>
+  <si>
+    <t>ITR Filing Deadline AY 2026-27 Latest Update | Haryana.Tools</t>
+  </si>
+  <si>
+    <t>Know the latest ITR due dates, extension news and filing tips with Haryana.Tools.</t>
+  </si>
+  <si>
+    <t>itr filing deadline,itr due date,july 31 itr,ay 2026-27</t>
+  </si>
+  <si>
+    <t>income tax return,itr extension,deadline</t>
+  </si>
+  <si>
+    <t>https://www.haryana.tools/blog.html?id=itr-filing-deadline-ay-2026-27</t>
+  </si>
+  <si>
+    <t>ITR Filing Deadline AY 2026-27</t>
+  </si>
+  <si>
+    <t>Latest deadline updates and filing guidance.</t>
+  </si>
+  <si>
+    <t>ITR Deadline Update</t>
+  </si>
+  <si>
+    <t>Know the latest filing deadline.</t>
+  </si>
+  <si>
+    <t>late-filing-penalty-itr</t>
+  </si>
+  <si>
+    <t>itr-deadline-faq.md</t>
+  </si>
+  <si>
+    <t>Late Filing Penalty for Income Tax Return Explained</t>
+  </si>
+  <si>
+    <t>Penalty</t>
+  </si>
+  <si>
+    <t>late filing,234F,interest</t>
+  </si>
+  <si>
+    <t>https://images.unsplash.com/photo-1454165804606-c3d57bc86b40?w=1200</t>
+  </si>
+  <si>
+    <t>late-fee.webp</t>
+  </si>
+  <si>
+    <t>Tax penalty notice</t>
+  </si>
+  <si>
+    <t>Understand penalties, interest and consequences of filing ITR after the due date.</t>
+  </si>
+  <si>
+    <t>late-filing-penalty-itr.md</t>
+  </si>
+  <si>
+    <t>Late Filing Penalty for ITR Explained</t>
+  </si>
+  <si>
+    <t>Avoid unnecessary penalties by filing your return on time with Haryana.Tools.</t>
+  </si>
+  <si>
+    <t>234F penalty,late itr fee,interest on tax</t>
+  </si>
+  <si>
+    <t>late filing penalty,income tax penalty</t>
+  </si>
+  <si>
+    <t>https://www.haryana.tools/blog.html?id=late-filing-penalty-itr</t>
+  </si>
+  <si>
+    <t>Late Filing Penalty</t>
+  </si>
+  <si>
+    <t>Understand late filing charges.</t>
+  </si>
+  <si>
+    <t>Late ITR Penalty</t>
+  </si>
+  <si>
+    <t>Avoid penalty by filing on time.</t>
+  </si>
+  <si>
+    <t>late-itr-faq.md</t>
+  </si>
+  <si>
+    <t>managed-service-provider-income-tax-portal</t>
+  </si>
+  <si>
+    <t>Why Was the Income Tax Portal Managed Service Provider Penalised?</t>
+  </si>
+  <si>
+    <t>Portal News</t>
+  </si>
+  <si>
+    <t>managed service provider,income tax portal,cbdt</t>
+  </si>
+  <si>
+    <t>https://images.unsplash.com/photo-1516321318423-f06f85e504b3?w=1200</t>
+  </si>
+  <si>
+    <t>portal-news.webp</t>
+  </si>
+  <si>
+    <t>Income tax portal dashboard</t>
+  </si>
+  <si>
+    <t>Learn why the managed service provider faced penalties and what has improved in the e-filing portal.</t>
+  </si>
+  <si>
+    <t>managed-service-provider-income-tax-portal.md</t>
+  </si>
+  <si>
+    <t>Managed Service Provider Penalty Explained</t>
+  </si>
+  <si>
+    <t>Understand the improvements made to the Income Tax e-filing portal.</t>
+  </si>
+  <si>
+    <t>managed service provider penalty,cbdt portal</t>
+  </si>
+  <si>
+    <t>income tax portal,efiling portal</t>
+  </si>
+  <si>
+    <t>https://www.haryana.tools/blog.html?id=managed-service-provider-income-tax-portal</t>
+  </si>
+  <si>
+    <t>Income Tax Portal Improvements</t>
+  </si>
+  <si>
+    <t>Portal performance and MSP penalty explained.</t>
+  </si>
+  <si>
+    <t>Income Tax Portal</t>
+  </si>
+  <si>
+    <t>Portal updates explained.</t>
+  </si>
+  <si>
+    <t>portal-faq.md</t>
+  </si>
+  <si>
+    <t>NewsArticle</t>
+  </si>
+  <si>
+    <t>how-to-file-itr-online</t>
+  </si>
+  <si>
+    <t>Step-by-Step Guide to File Income Tax Return Online</t>
+  </si>
+  <si>
+    <t>Guide</t>
+  </si>
+  <si>
+    <t>file itr online,efiling</t>
+  </si>
+  <si>
+    <t>https://images.unsplash.com/photo-1520607162513-77705c0f0d4a?w=1200</t>
+  </si>
+  <si>
+    <t>itr-guide.webp</t>
+  </si>
+  <si>
+    <t>Online tax filing</t>
+  </si>
+  <si>
+    <t>Complete guide to filing ITR online without mistakes.</t>
+  </si>
+  <si>
+    <t>how-to-file-itr-online.md</t>
+  </si>
+  <si>
+    <t>How to File ITR Online</t>
+  </si>
+  <si>
+    <t>Learn to file your Income Tax Return online with Haryana.Tools assistance.</t>
+  </si>
+  <si>
+    <t>file itr online,online itr filing</t>
+  </si>
+  <si>
+    <t>how to file itr</t>
+  </si>
+  <si>
+    <t>https://www.haryana.tools/blog.html?id=how-to-file-itr-online</t>
+  </si>
+  <si>
+    <t>Simple step-by-step filing guide.</t>
+  </si>
+  <si>
+    <t>File ITR Online</t>
+  </si>
+  <si>
+    <t>Simple filing guide.</t>
+  </si>
+  <si>
+    <t>itr-online-faq.md</t>
+  </si>
+  <si>
+    <t>HowTo</t>
+  </si>
+  <si>
+    <t>common-itr-filing-mistakes</t>
+  </si>
+  <si>
+    <t>15 Common ITR Filing Mistakes That Delay Your Refund</t>
+  </si>
+  <si>
+    <t>Tips</t>
+  </si>
+  <si>
+    <t>itr mistakes,refund delay</t>
+  </si>
+  <si>
+    <t>https://images.unsplash.com/photo-1554224154-26032ffc0d07?w=1200</t>
+  </si>
+  <si>
+    <t>refund.webp</t>
+  </si>
+  <si>
+    <t>Income tax refund</t>
+  </si>
+  <si>
+    <t>Avoid common filing errors that trigger notices or refund delays.</t>
+  </si>
+  <si>
+    <t>common-itr-filing-mistakes.md</t>
+  </si>
+  <si>
+    <t>Common ITR Filing Mistakes</t>
+  </si>
+  <si>
+    <t>Avoid refund delays with these expert tax filing tips.</t>
+  </si>
+  <si>
+    <t>refund,status</t>
+  </si>
+  <si>
+    <t>https://www.haryana.tools/blog.html?id=common-itr-filing-mistakes</t>
+  </si>
+  <si>
+    <t>Common ITR Mistakes</t>
+  </si>
+  <si>
+    <t>Avoid common filing errors.</t>
+  </si>
+  <si>
+    <t>ITR Mistakes</t>
+  </si>
+  <si>
+    <t>Avoid refund delay.</t>
+  </si>
+  <si>
+    <t>itr-mistakes-faq.md</t>
+  </si>
+  <si>
+    <t>ais-form26as-tis-check</t>
+  </si>
+  <si>
+    <t>How to Check AIS, Form 26AS &amp; TIS Before Filing ITR</t>
+  </si>
+  <si>
+    <t>Compliance</t>
+  </si>
+  <si>
+    <t>AIS,26AS,TIS</t>
+  </si>
+  <si>
+    <t>https://images.unsplash.com/photo-1450101499163-c8848c66ca85?w=1200</t>
+  </si>
+  <si>
+    <t>ais.webp</t>
+  </si>
+  <si>
+    <t>Financial statements</t>
+  </si>
+  <si>
+    <t>Learn how to verify AIS, Form 26AS and TIS before submitting your return.</t>
+  </si>
+  <si>
+    <t>ais-form26as-tis-check.md</t>
+  </si>
+  <si>
+    <t>Check AIS, Form 26AS &amp; TIS Before Filing ITR</t>
+  </si>
+  <si>
+    <t>Verify tax information before filing your return.</t>
+  </si>
+  <si>
+    <t>AIS,26AS,TIS,itr</t>
+  </si>
+  <si>
+    <t>form26as,ais,tis</t>
+  </si>
+  <si>
+    <t>https://www.haryana.tools/blog.html?id=ais-form26as-tis-check</t>
+  </si>
+  <si>
+    <t>AIS &amp; Form 26AS Guide</t>
+  </si>
+  <si>
+    <t>Check your tax information correctly.</t>
+  </si>
+  <si>
+    <t>AIS Guide</t>
+  </si>
+  <si>
+    <t>Verify before filing.</t>
+  </si>
+  <si>
+    <t>ais-faq.md</t>
+  </si>
+  <si>
+    <t>itr-notice-143-1</t>
+  </si>
+  <si>
+    <t>Received Income Tax Notice Under Section 143(1)? Here's What to Do</t>
+  </si>
+  <si>
+    <t>Notices</t>
+  </si>
+  <si>
+    <t>143(1),notice</t>
+  </si>
+  <si>
+    <t>https://images.unsplash.com/photo-1554224154-22dec7ec8818?w=1200</t>
+  </si>
+  <si>
+    <t>notice.webp</t>
+  </si>
+  <si>
+    <t>Income tax notice</t>
+  </si>
+  <si>
+    <t>Understand Section 143(1) intimation and how to respond.</t>
+  </si>
+  <si>
+    <t>itr-notice-143-1.md</t>
+  </si>
+  <si>
+    <t>Income Tax Notice 143(1) Guide</t>
+  </si>
+  <si>
+    <t>Everything you need to know about Section 143(1).</t>
+  </si>
+  <si>
+    <t>143(1) notice,income tax notice</t>
+  </si>
+  <si>
+    <t>income tax intimation</t>
+  </si>
+  <si>
+    <t>https://www.haryana.tools/blog.html?id=itr-notice-143-1</t>
+  </si>
+  <si>
+    <t>Section 143(1) Notice</t>
+  </si>
+  <si>
+    <t>Know what your intimation means.</t>
+  </si>
+  <si>
+    <t>143(1) Notice</t>
+  </si>
+  <si>
+    <t>Understand your notice.</t>
+  </si>
+  <si>
+    <t>1431-faq.md</t>
+  </si>
+  <si>
+    <t>best-online-itr-filing-service</t>
+  </si>
+  <si>
+    <t>Best Online ITR Filing Service in India</t>
+  </si>
+  <si>
+    <t>Services</t>
+  </si>
+  <si>
+    <t>itr filing service,online tax filing</t>
+  </si>
+  <si>
+    <t>https://images.unsplash.com/photo-1556740749-887f6717d7e4?w=1200</t>
+  </si>
+  <si>
+    <t>service.webp</t>
+  </si>
+  <si>
+    <t>Professional tax consultant</t>
+  </si>
+  <si>
+    <t>Looking for help filing your ITR? Haryana.Tools offers online filing assistance.</t>
+  </si>
+  <si>
+    <t>best-online-itr-filing-service.md</t>
+  </si>
+  <si>
+    <t>Best Online ITR Filing Assistance</t>
+  </si>
+  <si>
+    <t>Get professional ITR filing support from Haryana.Tools.</t>
+  </si>
+  <si>
+    <t>itr filing service,online itr help</t>
+  </si>
+  <si>
+    <t>itr consultant,itr filing online</t>
+  </si>
+  <si>
+    <t>https://www.haryana.tools/blog.html?id=best-online-itr-filing-service</t>
+  </si>
+  <si>
+    <t>Best Online ITR Filing Service</t>
+  </si>
+  <si>
+    <t>Professional filing assistance.</t>
+  </si>
+  <si>
+    <t>ITR Filing Help</t>
+  </si>
+  <si>
+    <t>Professional assistance.</t>
+  </si>
+  <si>
+    <t>itr-service-faq.md</t>
+  </si>
+  <si>
+    <t>Service</t>
+  </si>
+  <si>
+    <t>itr-for-small-business</t>
+  </si>
+  <si>
+    <t>ITR Filing Guide for Small Businesses and MSMEs</t>
+  </si>
+  <si>
+    <t>Business Tax</t>
+  </si>
+  <si>
+    <t>business itr,msme</t>
+  </si>
+  <si>
+    <t>https://images.unsplash.com/photo-1521791136064-7986c2920216?w=1200</t>
+  </si>
+  <si>
+    <t>business.webp</t>
+  </si>
+  <si>
+    <t>Small business accounting</t>
+  </si>
+  <si>
+    <t>Everything MSMEs should know before filing business income tax returns.</t>
+  </si>
+  <si>
+    <t>itr-for-small-business.md</t>
+  </si>
+  <si>
+    <t>Small Business ITR Guide</t>
+  </si>
+  <si>
+    <t>Complete guide for MSMEs and proprietors.</t>
+  </si>
+  <si>
+    <t>business itr,msme tax</t>
+  </si>
+  <si>
+    <t>business return</t>
+  </si>
+  <si>
+    <t>https://www.haryana.tools/blog.html?id=itr-for-small-business</t>
+  </si>
+  <si>
+    <t>MSME ITR Guide</t>
+  </si>
+  <si>
+    <t>Business tax filing simplified.</t>
+  </si>
+  <si>
+    <t>Business ITR</t>
+  </si>
+  <si>
+    <t>Guide for MSMEs.</t>
+  </si>
+  <si>
+    <t>business-itr-faq.md</t>
+  </si>
+  <si>
+    <t>itr-for-freelancers</t>
+  </si>
+  <si>
+    <t>Income Tax Return Guide for Freelancers and Professionals</t>
+  </si>
+  <si>
+    <t>Freelancer Tax</t>
+  </si>
+  <si>
+    <t>freelancer itr,professional tax</t>
+  </si>
+  <si>
+    <t>https://images.unsplash.com/photo-1498050108023-c5249f4df085?w=1200</t>
+  </si>
+  <si>
+    <t>freelancer.webp</t>
+  </si>
+  <si>
+    <t>Freelancer working</t>
+  </si>
+  <si>
+    <t>Understand ITR forms, deductions and compliance for freelancers.</t>
+  </si>
+  <si>
+    <t>itr-for-freelancers.md</t>
+  </si>
+  <si>
+    <t>Freelancer ITR Guide</t>
+  </si>
+  <si>
+    <t>Complete freelancer tax filing guide.</t>
+  </si>
+  <si>
+    <t>consultant tax</t>
+  </si>
+  <si>
+    <t>https://www.haryana.tools/blog.html?id=itr-for-freelancers</t>
+  </si>
+  <si>
+    <t>Tax filing made easy.</t>
+  </si>
+  <si>
+    <t>Easy filing guide.</t>
+  </si>
+  <si>
+    <t>freelancer-faq.md</t>
+  </si>
+  <si>
+    <t>income-tax-refund-delay</t>
+  </si>
+  <si>
+    <t>Why Is My Income Tax Refund Delayed?</t>
+  </si>
+  <si>
+    <t>Refund</t>
+  </si>
+  <si>
+    <t>tax refund,refund status</t>
+  </si>
+  <si>
+    <t>https://images.unsplash.com/photo-1554224155-8d04cb21cd6c?w=1200</t>
+  </si>
+  <si>
+    <t>refund-delay.webp</t>
+  </si>
+  <si>
+    <t>Tax refund process</t>
+  </si>
+  <si>
+    <t>Top reasons for delayed refunds and how to fix them.</t>
+  </si>
+  <si>
+    <t>income-tax-refund-delay.md</t>
+  </si>
+  <si>
+    <t>Income Tax Refund Delay Guide</t>
+  </si>
+  <si>
+    <t>Track and resolve refund delays.</t>
+  </si>
+  <si>
+    <t>income tax refund delayed</t>
+  </si>
+  <si>
+    <t>refund status</t>
+  </si>
+  <si>
+    <t>https://www.haryana.tools/blog.html?id=income-tax-refund-delay</t>
+  </si>
+  <si>
+    <t>Income Tax Refund Delay</t>
+  </si>
+  <si>
+    <t>Understand refund processing.</t>
+  </si>
+  <si>
+    <t>Refund Delay</t>
+  </si>
+  <si>
+    <t>Know the reasons.</t>
+  </si>
+  <si>
+    <t>refund-faq.md</t>
+  </si>
+  <si>
+    <t>why-choose-haryana-tools-for-itr</t>
+  </si>
+  <si>
+    <t>Why Choose Haryana.Tools for Online ITR Filing Assistance?</t>
+  </si>
+  <si>
+    <t>itr service,haryana.tools,tax filing</t>
+  </si>
+  <si>
+    <t>haryana-tools-itr.webp</t>
+  </si>
+  <si>
+    <t>Online tax filing assistance</t>
+  </si>
+  <si>
+    <t>Discover how Haryana.Tools helps individuals and businesses file Income Tax Returns online quickly and accurately.</t>
+  </si>
+  <si>
+    <t>why-choose-haryana-tools-for-itr.md</t>
+  </si>
+  <si>
+    <t>Online ITR Filing Assistance | Haryana.Tools</t>
+  </si>
+  <si>
+    <t>Need help filing your ITR? Haryana.Tools offers online tax filing assistance, document review, AIS checking, Form 26AS verification and support throughout the filing process.</t>
+  </si>
+  <si>
+    <t>online itr filing assistance,haryana.tools itr filing,income tax consultant,itr help</t>
+  </si>
+  <si>
+    <t>itr filing service near me,online itr filing,tax filing help,form 26as help,ais verification</t>
+  </si>
+  <si>
+    <t>https://www.haryana.tools/blog.html?id=why-choose-haryana-tools-for-itr</t>
+  </si>
+  <si>
+    <t>Why Haryana.Tools for ITR?</t>
+  </si>
+  <si>
+    <t>Professional online tax filing assistance.</t>
+  </si>
+  <si>
+    <t>ITR Filing Assistance</t>
+  </si>
+  <si>
+    <t>Get expert help with your return.</t>
+  </si>
+  <si>
+    <t>haryana-tools-itr-faq.md</t>
+  </si>
+  <si>
+    <t>BLOG0125</t>
+  </si>
+  <si>
+    <t>BLOG0126</t>
+  </si>
+  <si>
+    <t>BLOG0127</t>
+  </si>
+  <si>
+    <t>BLOG0128</t>
+  </si>
+  <si>
+    <t>BLOG0129</t>
+  </si>
+  <si>
+    <t>BLOG0130</t>
+  </si>
+  <si>
+    <t>BLOG0131</t>
+  </si>
+  <si>
+    <t>BLOG0132</t>
+  </si>
+  <si>
+    <t>BLOG0133</t>
+  </si>
+  <si>
+    <t>BLOG0134</t>
+  </si>
+  <si>
+    <t>BLOG0135</t>
+  </si>
+  <si>
+    <t>BLOG0136</t>
   </si>
 </sst>
 </file>
@@ -7390,7 +8101,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -7403,6 +8114,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -7740,7 +8452,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A8F2F70-D1BF-44E2-90B8-B0E4DAB2F558}">
-  <dimension ref="A1:AK125"/>
+  <dimension ref="A1:AK138"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="9" max="9" width="11.5546875" style="8" bestFit="1" customWidth="1"/>
@@ -17846,11 +18558,11 @@
       <c r="AA91" s="3" t="s">
         <v>1841</v>
       </c>
-      <c r="AB91" s="11" t="s">
+      <c r="AB91" s="12" t="s">
         <v>1488</v>
       </c>
-      <c r="AC91" s="12"/>
-      <c r="AD91" s="12"/>
+      <c r="AC91" s="13"/>
+      <c r="AD91" s="13"/>
       <c r="AE91" s="5" t="s">
         <v>1847</v>
       </c>
@@ -17955,11 +18667,11 @@
       <c r="AA92" s="3" t="s">
         <v>1855</v>
       </c>
-      <c r="AB92" s="11" t="s">
+      <c r="AB92" s="12" t="s">
         <v>1488</v>
       </c>
-      <c r="AC92" s="12"/>
-      <c r="AD92" s="12"/>
+      <c r="AC92" s="13"/>
+      <c r="AD92" s="13"/>
       <c r="AE92" s="5" t="s">
         <v>1861</v>
       </c>
@@ -18064,11 +18776,11 @@
       <c r="AA93" s="3" t="s">
         <v>1869</v>
       </c>
-      <c r="AB93" s="11" t="s">
+      <c r="AB93" s="12" t="s">
         <v>1488</v>
       </c>
-      <c r="AC93" s="12"/>
-      <c r="AD93" s="12"/>
+      <c r="AC93" s="13"/>
+      <c r="AD93" s="13"/>
       <c r="AE93" s="5" t="s">
         <v>1875</v>
       </c>
@@ -18173,11 +18885,11 @@
       <c r="AA94" s="3" t="s">
         <v>1881</v>
       </c>
-      <c r="AB94" s="11" t="s">
+      <c r="AB94" s="12" t="s">
         <v>1488</v>
       </c>
-      <c r="AC94" s="12"/>
-      <c r="AD94" s="12"/>
+      <c r="AC94" s="13"/>
+      <c r="AD94" s="13"/>
       <c r="AE94" s="5" t="s">
         <v>1885</v>
       </c>
@@ -18282,11 +18994,11 @@
       <c r="AA95" s="3" t="s">
         <v>1881</v>
       </c>
-      <c r="AB95" s="11" t="s">
+      <c r="AB95" s="12" t="s">
         <v>1488</v>
       </c>
-      <c r="AC95" s="12"/>
-      <c r="AD95" s="12"/>
+      <c r="AC95" s="13"/>
+      <c r="AD95" s="13"/>
       <c r="AE95" s="5" t="s">
         <v>1894</v>
       </c>
@@ -18391,11 +19103,11 @@
       <c r="AA96" s="3" t="s">
         <v>1902</v>
       </c>
-      <c r="AB96" s="11" t="s">
+      <c r="AB96" s="12" t="s">
         <v>1488</v>
       </c>
-      <c r="AC96" s="12"/>
-      <c r="AD96" s="12"/>
+      <c r="AC96" s="13"/>
+      <c r="AD96" s="13"/>
       <c r="AE96" s="5" t="s">
         <v>1908</v>
       </c>
@@ -18500,11 +19212,11 @@
       <c r="AA97" s="3" t="s">
         <v>1916</v>
       </c>
-      <c r="AB97" s="11" t="s">
+      <c r="AB97" s="12" t="s">
         <v>1488</v>
       </c>
-      <c r="AC97" s="12"/>
-      <c r="AD97" s="12"/>
+      <c r="AC97" s="13"/>
+      <c r="AD97" s="13"/>
       <c r="AE97" s="5" t="s">
         <v>1922</v>
       </c>
@@ -18609,11 +19321,11 @@
       <c r="AA98" s="3" t="s">
         <v>1928</v>
       </c>
-      <c r="AB98" s="11" t="s">
+      <c r="AB98" s="12" t="s">
         <v>1488</v>
       </c>
-      <c r="AC98" s="12"/>
-      <c r="AD98" s="12"/>
+      <c r="AC98" s="13"/>
+      <c r="AD98" s="13"/>
       <c r="AE98" s="5" t="s">
         <v>1932</v>
       </c>
@@ -18718,11 +19430,11 @@
       <c r="AA99" s="3" t="s">
         <v>1939</v>
       </c>
-      <c r="AB99" s="11" t="s">
+      <c r="AB99" s="12" t="s">
         <v>1488</v>
       </c>
-      <c r="AC99" s="12"/>
-      <c r="AD99" s="12"/>
+      <c r="AC99" s="13"/>
+      <c r="AD99" s="13"/>
       <c r="AE99" s="5" t="s">
         <v>1945</v>
       </c>
@@ -18827,11 +19539,11 @@
       <c r="AA100" s="3" t="s">
         <v>1952</v>
       </c>
-      <c r="AB100" s="11" t="s">
+      <c r="AB100" s="12" t="s">
         <v>1488</v>
       </c>
-      <c r="AC100" s="12"/>
-      <c r="AD100" s="12"/>
+      <c r="AC100" s="13"/>
+      <c r="AD100" s="13"/>
       <c r="AE100" s="5" t="s">
         <v>1958</v>
       </c>
@@ -18936,11 +19648,11 @@
       <c r="AA101" s="3" t="s">
         <v>1966</v>
       </c>
-      <c r="AB101" s="11" t="s">
+      <c r="AB101" s="12" t="s">
         <v>1488</v>
       </c>
-      <c r="AC101" s="12"/>
-      <c r="AD101" s="12"/>
+      <c r="AC101" s="13"/>
+      <c r="AD101" s="13"/>
       <c r="AE101" s="5" t="s">
         <v>1972</v>
       </c>
@@ -19045,11 +19757,11 @@
       <c r="AA102" s="3" t="s">
         <v>1979</v>
       </c>
-      <c r="AB102" s="11" t="s">
+      <c r="AB102" s="12" t="s">
         <v>1488</v>
       </c>
-      <c r="AC102" s="12"/>
-      <c r="AD102" s="12"/>
+      <c r="AC102" s="13"/>
+      <c r="AD102" s="13"/>
       <c r="AE102" s="5" t="s">
         <v>1985</v>
       </c>
@@ -19154,11 +19866,11 @@
       <c r="AA103" s="3" t="s">
         <v>1991</v>
       </c>
-      <c r="AB103" s="11" t="s">
+      <c r="AB103" s="12" t="s">
         <v>1488</v>
       </c>
-      <c r="AC103" s="12"/>
-      <c r="AD103" s="12"/>
+      <c r="AC103" s="13"/>
+      <c r="AD103" s="13"/>
       <c r="AE103" s="5" t="s">
         <v>1995</v>
       </c>
@@ -19207,10 +19919,10 @@
         <v>44</v>
       </c>
       <c r="I104" s="8">
-        <v>46226</v>
+        <v>46225</v>
       </c>
       <c r="J104" s="8">
-        <v>46226</v>
+        <v>46225</v>
       </c>
       <c r="K104" s="3" t="s">
         <v>45</v>
@@ -19263,11 +19975,11 @@
       <c r="AA104" s="3" t="s">
         <v>2002</v>
       </c>
-      <c r="AB104" s="11" t="s">
+      <c r="AB104" s="12" t="s">
         <v>1488</v>
       </c>
-      <c r="AC104" s="12"/>
-      <c r="AD104" s="12"/>
+      <c r="AC104" s="13"/>
+      <c r="AD104" s="13"/>
       <c r="AE104" s="5" t="s">
         <v>2008</v>
       </c>
@@ -19316,10 +20028,10 @@
         <v>44</v>
       </c>
       <c r="I105" s="8">
-        <v>46227</v>
+        <v>46225</v>
       </c>
       <c r="J105" s="8">
-        <v>46227</v>
+        <v>46225</v>
       </c>
       <c r="K105" s="3" t="s">
         <v>45</v>
@@ -19372,11 +20084,11 @@
       <c r="AA105" s="3" t="s">
         <v>2013</v>
       </c>
-      <c r="AB105" s="11" t="s">
+      <c r="AB105" s="12" t="s">
         <v>1488</v>
       </c>
-      <c r="AC105" s="12"/>
-      <c r="AD105" s="12"/>
+      <c r="AC105" s="13"/>
+      <c r="AD105" s="13"/>
       <c r="AE105" s="5" t="s">
         <v>2017</v>
       </c>
@@ -19425,10 +20137,10 @@
         <v>44</v>
       </c>
       <c r="I106" s="8">
-        <v>46228</v>
+        <v>46225</v>
       </c>
       <c r="J106" s="8">
-        <v>46228</v>
+        <v>46225</v>
       </c>
       <c r="K106" s="3" t="s">
         <v>45</v>
@@ -19481,11 +20193,11 @@
       <c r="AA106" s="3" t="s">
         <v>2025</v>
       </c>
-      <c r="AB106" s="11" t="s">
+      <c r="AB106" s="12" t="s">
         <v>1488</v>
       </c>
-      <c r="AC106" s="12"/>
-      <c r="AD106" s="12"/>
+      <c r="AC106" s="13"/>
+      <c r="AD106" s="13"/>
       <c r="AE106" s="5" t="s">
         <v>2031</v>
       </c>
@@ -19534,10 +20246,10 @@
         <v>44</v>
       </c>
       <c r="I107" s="8">
-        <v>46228</v>
+        <v>46225</v>
       </c>
       <c r="J107" s="8">
-        <v>46228</v>
+        <v>46225</v>
       </c>
       <c r="K107" s="3" t="s">
         <v>45</v>
@@ -19590,11 +20302,11 @@
       <c r="AA107" s="3" t="s">
         <v>2039</v>
       </c>
-      <c r="AB107" s="11" t="s">
+      <c r="AB107" s="12" t="s">
         <v>1488</v>
       </c>
-      <c r="AC107" s="12"/>
-      <c r="AD107" s="12"/>
+      <c r="AC107" s="13"/>
+      <c r="AD107" s="13"/>
       <c r="AE107" s="5" t="s">
         <v>2045</v>
       </c>
@@ -19643,10 +20355,10 @@
         <v>44</v>
       </c>
       <c r="I108" s="8">
-        <v>46229</v>
+        <v>46225</v>
       </c>
       <c r="J108" s="8">
-        <v>46229</v>
+        <v>46225</v>
       </c>
       <c r="K108" s="3" t="s">
         <v>45</v>
@@ -19699,11 +20411,11 @@
       <c r="AA108" s="3" t="s">
         <v>2053</v>
       </c>
-      <c r="AB108" s="11" t="s">
+      <c r="AB108" s="12" t="s">
         <v>1488</v>
       </c>
-      <c r="AC108" s="12"/>
-      <c r="AD108" s="12"/>
+      <c r="AC108" s="13"/>
+      <c r="AD108" s="13"/>
       <c r="AE108" s="5" t="s">
         <v>2059</v>
       </c>
@@ -19752,10 +20464,10 @@
         <v>44</v>
       </c>
       <c r="I109" s="8">
-        <v>46230</v>
+        <v>46225</v>
       </c>
       <c r="J109" s="8">
-        <v>46230</v>
+        <v>46225</v>
       </c>
       <c r="K109" s="3" t="s">
         <v>45</v>
@@ -19808,11 +20520,11 @@
       <c r="AA109" s="3" t="s">
         <v>2068</v>
       </c>
-      <c r="AB109" s="11" t="s">
+      <c r="AB109" s="12" t="s">
         <v>1488</v>
       </c>
-      <c r="AC109" s="12"/>
-      <c r="AD109" s="12"/>
+      <c r="AC109" s="13"/>
+      <c r="AD109" s="13"/>
       <c r="AE109" s="5" t="s">
         <v>2074</v>
       </c>
@@ -19861,10 +20573,10 @@
         <v>44</v>
       </c>
       <c r="I110" s="8">
-        <v>46230</v>
+        <v>46225</v>
       </c>
       <c r="J110" s="8">
-        <v>46230</v>
+        <v>46225</v>
       </c>
       <c r="K110" s="3" t="s">
         <v>45</v>
@@ -19917,11 +20629,11 @@
       <c r="AA110" s="3" t="s">
         <v>2080</v>
       </c>
-      <c r="AB110" s="11" t="s">
+      <c r="AB110" s="12" t="s">
         <v>1488</v>
       </c>
-      <c r="AC110" s="12"/>
-      <c r="AD110" s="12"/>
+      <c r="AC110" s="13"/>
+      <c r="AD110" s="13"/>
       <c r="AE110" s="5" t="s">
         <v>2086</v>
       </c>
@@ -19970,10 +20682,10 @@
         <v>44</v>
       </c>
       <c r="I111" s="8">
-        <v>46231</v>
+        <v>46225</v>
       </c>
       <c r="J111" s="8">
-        <v>46231</v>
+        <v>46225</v>
       </c>
       <c r="K111" s="7" t="s">
         <v>45</v>
@@ -20083,10 +20795,10 @@
         <v>44</v>
       </c>
       <c r="I112" s="8">
-        <v>46231</v>
+        <v>46225</v>
       </c>
       <c r="J112" s="8">
-        <v>46231</v>
+        <v>46225</v>
       </c>
       <c r="K112" s="7" t="s">
         <v>45</v>
@@ -20196,10 +20908,10 @@
         <v>44</v>
       </c>
       <c r="I113" s="8">
-        <v>46232</v>
+        <v>46225</v>
       </c>
       <c r="J113" s="8">
-        <v>46232</v>
+        <v>46225</v>
       </c>
       <c r="K113" s="7" t="s">
         <v>45</v>
@@ -20305,10 +21017,10 @@
         <v>44</v>
       </c>
       <c r="I114" s="8">
-        <v>46232</v>
+        <v>46226</v>
       </c>
       <c r="J114" s="8">
-        <v>46232</v>
+        <v>46226</v>
       </c>
       <c r="K114" s="7" t="s">
         <v>45</v>
@@ -20414,10 +21126,10 @@
         <v>44</v>
       </c>
       <c r="I115" s="8">
-        <v>46233</v>
+        <v>46226</v>
       </c>
       <c r="J115" s="8">
-        <v>46233</v>
+        <v>46226</v>
       </c>
       <c r="K115" s="7" t="s">
         <v>1756</v>
@@ -20527,10 +21239,10 @@
         <v>44</v>
       </c>
       <c r="I116" s="8">
-        <v>46233</v>
+        <v>46226</v>
       </c>
       <c r="J116" s="8">
-        <v>46233</v>
+        <v>46226</v>
       </c>
       <c r="K116" s="7" t="s">
         <v>1756</v>
@@ -20640,10 +21352,10 @@
         <v>44</v>
       </c>
       <c r="I117" s="8">
-        <v>46234</v>
+        <v>46226</v>
       </c>
       <c r="J117" s="8">
-        <v>46234</v>
+        <v>46226</v>
       </c>
       <c r="K117" s="7" t="s">
         <v>1756</v>
@@ -20753,10 +21465,10 @@
         <v>44</v>
       </c>
       <c r="I118" s="8">
-        <v>46234</v>
+        <v>46226</v>
       </c>
       <c r="J118" s="8">
-        <v>46234</v>
+        <v>46226</v>
       </c>
       <c r="K118" s="7" t="s">
         <v>1756</v>
@@ -20866,10 +21578,10 @@
         <v>44</v>
       </c>
       <c r="I119" s="8">
-        <v>46234</v>
+        <v>46226</v>
       </c>
       <c r="J119" s="8">
-        <v>46234</v>
+        <v>46226</v>
       </c>
       <c r="K119" s="7" t="s">
         <v>1756</v>
@@ -20979,10 +21691,10 @@
         <v>44</v>
       </c>
       <c r="I120" s="8">
-        <v>46234</v>
+        <v>46226</v>
       </c>
       <c r="J120" s="8">
-        <v>46234</v>
+        <v>46226</v>
       </c>
       <c r="K120" s="7" t="s">
         <v>1756</v>
@@ -21092,10 +21804,10 @@
         <v>44</v>
       </c>
       <c r="I121" s="8">
-        <v>46234</v>
+        <v>46226</v>
       </c>
       <c r="J121" s="8">
-        <v>46234</v>
+        <v>46226</v>
       </c>
       <c r="K121" s="7" t="s">
         <v>1756</v>
@@ -21205,10 +21917,10 @@
         <v>44</v>
       </c>
       <c r="I122" s="8">
-        <v>46234</v>
+        <v>46226</v>
       </c>
       <c r="J122" s="8">
-        <v>46234</v>
+        <v>46226</v>
       </c>
       <c r="K122" s="7" t="s">
         <v>1756</v>
@@ -21318,10 +22030,10 @@
         <v>44</v>
       </c>
       <c r="I123" s="8">
-        <v>46234</v>
+        <v>46226</v>
       </c>
       <c r="J123" s="8">
-        <v>46234</v>
+        <v>46226</v>
       </c>
       <c r="K123" s="7" t="s">
         <v>45</v>
@@ -21427,10 +22139,10 @@
         <v>44</v>
       </c>
       <c r="I124" s="8">
-        <v>46234</v>
+        <v>46226</v>
       </c>
       <c r="J124" s="8">
-        <v>46234</v>
+        <v>46226</v>
       </c>
       <c r="K124" s="7" t="s">
         <v>45</v>
@@ -21536,10 +22248,10 @@
         <v>44</v>
       </c>
       <c r="I125" s="8">
-        <v>46234</v>
+        <v>46226</v>
       </c>
       <c r="J125" s="8">
-        <v>46234</v>
+        <v>46226</v>
       </c>
       <c r="K125" s="7" t="s">
         <v>45</v>
@@ -21619,16 +22331,1319 @@
         <v>124</v>
       </c>
     </row>
+    <row r="126" spans="1:37" s="11" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A126" s="1" t="s">
+        <v>2586</v>
+      </c>
+      <c r="B126" s="11" t="s">
+        <v>2361</v>
+      </c>
+      <c r="C126" s="11" t="s">
+        <v>2362</v>
+      </c>
+      <c r="D126" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="E126" s="11" t="s">
+        <v>2363</v>
+      </c>
+      <c r="F126" s="11" t="s">
+        <v>2364</v>
+      </c>
+      <c r="G126" s="11" t="s">
+        <v>2365</v>
+      </c>
+      <c r="H126" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="I126" s="8">
+        <v>46227</v>
+      </c>
+      <c r="J126" s="8">
+        <v>46227</v>
+      </c>
+      <c r="K126" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="L126" s="11">
+        <v>6</v>
+      </c>
+      <c r="M126" s="11" t="s">
+        <v>2366</v>
+      </c>
+      <c r="N126" s="11" t="s">
+        <v>2367</v>
+      </c>
+      <c r="O126" s="11" t="s">
+        <v>2368</v>
+      </c>
+      <c r="P126" s="11" t="s">
+        <v>2369</v>
+      </c>
+      <c r="Q126" s="11" t="s">
+        <v>2370</v>
+      </c>
+      <c r="R126" s="11" t="s">
+        <v>2371</v>
+      </c>
+      <c r="S126" s="11" t="s">
+        <v>2372</v>
+      </c>
+      <c r="T126" s="11" t="s">
+        <v>2373</v>
+      </c>
+      <c r="U126" s="11" t="s">
+        <v>2374</v>
+      </c>
+      <c r="V126" s="11" t="s">
+        <v>2375</v>
+      </c>
+      <c r="W126" s="11" t="s">
+        <v>2376</v>
+      </c>
+      <c r="X126" s="11" t="s">
+        <v>2377</v>
+      </c>
+      <c r="Y126" s="11" t="s">
+        <v>2366</v>
+      </c>
+      <c r="Z126" s="11" t="s">
+        <v>2378</v>
+      </c>
+      <c r="AA126" s="11" t="s">
+        <v>2379</v>
+      </c>
+      <c r="AB126" s="11" t="s">
+        <v>2366</v>
+      </c>
+      <c r="AD126" s="11" t="s">
+        <v>2380</v>
+      </c>
+      <c r="AE126" s="11" t="s">
+        <v>2381</v>
+      </c>
+      <c r="AF126" s="11">
+        <v>1</v>
+      </c>
+      <c r="AG126" s="11">
+        <v>0</v>
+      </c>
+      <c r="AH126" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="AI126" s="11" t="s">
+        <v>2175</v>
+      </c>
+      <c r="AJ126" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="AK126" s="1">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="127" spans="1:37" s="11" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A127" s="1" t="s">
+        <v>2587</v>
+      </c>
+      <c r="B127" s="11" t="s">
+        <v>2380</v>
+      </c>
+      <c r="C127" s="11" t="s">
+        <v>2382</v>
+      </c>
+      <c r="D127" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="E127" s="11" t="s">
+        <v>2363</v>
+      </c>
+      <c r="F127" s="11" t="s">
+        <v>2383</v>
+      </c>
+      <c r="G127" s="11" t="s">
+        <v>2384</v>
+      </c>
+      <c r="H127" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="I127" s="8">
+        <v>46227</v>
+      </c>
+      <c r="J127" s="8">
+        <v>46227</v>
+      </c>
+      <c r="K127" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="L127" s="11">
+        <v>7</v>
+      </c>
+      <c r="M127" s="11" t="s">
+        <v>2385</v>
+      </c>
+      <c r="N127" s="11" t="s">
+        <v>2386</v>
+      </c>
+      <c r="O127" s="11" t="s">
+        <v>2387</v>
+      </c>
+      <c r="P127" s="11" t="s">
+        <v>2388</v>
+      </c>
+      <c r="Q127" s="11" t="s">
+        <v>2389</v>
+      </c>
+      <c r="R127" s="11" t="s">
+        <v>2390</v>
+      </c>
+      <c r="S127" s="11" t="s">
+        <v>2391</v>
+      </c>
+      <c r="T127" s="11" t="s">
+        <v>2392</v>
+      </c>
+      <c r="U127" s="11" t="s">
+        <v>2393</v>
+      </c>
+      <c r="V127" s="11" t="s">
+        <v>2394</v>
+      </c>
+      <c r="W127" s="11" t="s">
+        <v>2395</v>
+      </c>
+      <c r="X127" s="11" t="s">
+        <v>2396</v>
+      </c>
+      <c r="Y127" s="11" t="s">
+        <v>2385</v>
+      </c>
+      <c r="Z127" s="11" t="s">
+        <v>2397</v>
+      </c>
+      <c r="AA127" s="11" t="s">
+        <v>2398</v>
+      </c>
+      <c r="AB127" s="11" t="s">
+        <v>2385</v>
+      </c>
+      <c r="AD127" s="11" t="s">
+        <v>2361</v>
+      </c>
+      <c r="AE127" s="11" t="s">
+        <v>2399</v>
+      </c>
+      <c r="AF127" s="11">
+        <v>1</v>
+      </c>
+      <c r="AG127" s="11">
+        <v>0</v>
+      </c>
+      <c r="AH127" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="AI127" s="11" t="s">
+        <v>2175</v>
+      </c>
+      <c r="AJ127" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="AK127" s="1">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="128" spans="1:37" s="11" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A128" s="1" t="s">
+        <v>2588</v>
+      </c>
+      <c r="B128" s="11" t="s">
+        <v>2400</v>
+      </c>
+      <c r="C128" s="11" t="s">
+        <v>2401</v>
+      </c>
+      <c r="D128" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="E128" s="11" t="s">
+        <v>2363</v>
+      </c>
+      <c r="F128" s="11" t="s">
+        <v>2402</v>
+      </c>
+      <c r="G128" s="11" t="s">
+        <v>2403</v>
+      </c>
+      <c r="H128" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="I128" s="8">
+        <v>46227</v>
+      </c>
+      <c r="J128" s="8">
+        <v>46227</v>
+      </c>
+      <c r="K128" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="L128" s="11">
+        <v>5</v>
+      </c>
+      <c r="M128" s="11" t="s">
+        <v>2404</v>
+      </c>
+      <c r="N128" s="11" t="s">
+        <v>2405</v>
+      </c>
+      <c r="O128" s="11" t="s">
+        <v>2406</v>
+      </c>
+      <c r="P128" s="11" t="s">
+        <v>2407</v>
+      </c>
+      <c r="Q128" s="11" t="s">
+        <v>2408</v>
+      </c>
+      <c r="R128" s="11" t="s">
+        <v>2409</v>
+      </c>
+      <c r="S128" s="11" t="s">
+        <v>2410</v>
+      </c>
+      <c r="T128" s="11" t="s">
+        <v>2411</v>
+      </c>
+      <c r="U128" s="11" t="s">
+        <v>2412</v>
+      </c>
+      <c r="V128" s="11" t="s">
+        <v>2413</v>
+      </c>
+      <c r="W128" s="11" t="s">
+        <v>2414</v>
+      </c>
+      <c r="X128" s="11" t="s">
+        <v>2415</v>
+      </c>
+      <c r="Y128" s="11" t="s">
+        <v>2404</v>
+      </c>
+      <c r="Z128" s="11" t="s">
+        <v>2416</v>
+      </c>
+      <c r="AA128" s="11" t="s">
+        <v>2417</v>
+      </c>
+      <c r="AB128" s="11" t="s">
+        <v>2404</v>
+      </c>
+      <c r="AD128" s="11" t="s">
+        <v>2361</v>
+      </c>
+      <c r="AE128" s="11" t="s">
+        <v>2418</v>
+      </c>
+      <c r="AF128" s="11">
+        <v>0.9</v>
+      </c>
+      <c r="AG128" s="11">
+        <v>0</v>
+      </c>
+      <c r="AH128" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="AI128" s="11" t="s">
+        <v>2419</v>
+      </c>
+      <c r="AJ128" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="AK128" s="1">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="129" spans="1:37" s="11" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A129" s="1" t="s">
+        <v>2589</v>
+      </c>
+      <c r="B129" s="11" t="s">
+        <v>2420</v>
+      </c>
+      <c r="C129" s="11" t="s">
+        <v>2421</v>
+      </c>
+      <c r="D129" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="E129" s="11" t="s">
+        <v>2363</v>
+      </c>
+      <c r="F129" s="11" t="s">
+        <v>2422</v>
+      </c>
+      <c r="G129" s="11" t="s">
+        <v>2423</v>
+      </c>
+      <c r="H129" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="I129" s="8">
+        <v>46227</v>
+      </c>
+      <c r="J129" s="8">
+        <v>46227</v>
+      </c>
+      <c r="K129" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="L129" s="11">
+        <v>9</v>
+      </c>
+      <c r="M129" s="11" t="s">
+        <v>2424</v>
+      </c>
+      <c r="N129" s="11" t="s">
+        <v>2425</v>
+      </c>
+      <c r="O129" s="11" t="s">
+        <v>2426</v>
+      </c>
+      <c r="P129" s="11" t="s">
+        <v>2427</v>
+      </c>
+      <c r="Q129" s="11" t="s">
+        <v>2428</v>
+      </c>
+      <c r="R129" s="11" t="s">
+        <v>2429</v>
+      </c>
+      <c r="S129" s="11" t="s">
+        <v>2430</v>
+      </c>
+      <c r="T129" s="11" t="s">
+        <v>2431</v>
+      </c>
+      <c r="U129" s="11" t="s">
+        <v>2432</v>
+      </c>
+      <c r="V129" s="11" t="s">
+        <v>2433</v>
+      </c>
+      <c r="W129" s="11" t="s">
+        <v>2429</v>
+      </c>
+      <c r="X129" s="11" t="s">
+        <v>2434</v>
+      </c>
+      <c r="Y129" s="11" t="s">
+        <v>2424</v>
+      </c>
+      <c r="Z129" s="11" t="s">
+        <v>2435</v>
+      </c>
+      <c r="AA129" s="11" t="s">
+        <v>2436</v>
+      </c>
+      <c r="AB129" s="11" t="s">
+        <v>2424</v>
+      </c>
+      <c r="AD129" s="11" t="s">
+        <v>2380</v>
+      </c>
+      <c r="AE129" s="11" t="s">
+        <v>2437</v>
+      </c>
+      <c r="AF129" s="11">
+        <v>1</v>
+      </c>
+      <c r="AG129" s="11">
+        <v>0</v>
+      </c>
+      <c r="AH129" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="AI129" s="11" t="s">
+        <v>2438</v>
+      </c>
+      <c r="AJ129" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="AK129" s="1">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="130" spans="1:37" s="11" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A130" s="1" t="s">
+        <v>2590</v>
+      </c>
+      <c r="B130" s="11" t="s">
+        <v>2439</v>
+      </c>
+      <c r="C130" s="11" t="s">
+        <v>2440</v>
+      </c>
+      <c r="D130" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="E130" s="11" t="s">
+        <v>2363</v>
+      </c>
+      <c r="F130" s="11" t="s">
+        <v>2441</v>
+      </c>
+      <c r="G130" s="11" t="s">
+        <v>2442</v>
+      </c>
+      <c r="H130" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="I130" s="8">
+        <v>46227</v>
+      </c>
+      <c r="J130" s="8">
+        <v>46227</v>
+      </c>
+      <c r="K130" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="L130" s="11">
+        <v>7</v>
+      </c>
+      <c r="M130" s="11" t="s">
+        <v>2443</v>
+      </c>
+      <c r="N130" s="11" t="s">
+        <v>2444</v>
+      </c>
+      <c r="O130" s="11" t="s">
+        <v>2445</v>
+      </c>
+      <c r="P130" s="11" t="s">
+        <v>2446</v>
+      </c>
+      <c r="Q130" s="11" t="s">
+        <v>2447</v>
+      </c>
+      <c r="R130" s="11" t="s">
+        <v>2448</v>
+      </c>
+      <c r="S130" s="11" t="s">
+        <v>2449</v>
+      </c>
+      <c r="T130" s="11" t="s">
+        <v>2442</v>
+      </c>
+      <c r="U130" s="11" t="s">
+        <v>2450</v>
+      </c>
+      <c r="V130" s="11" t="s">
+        <v>2451</v>
+      </c>
+      <c r="W130" s="11" t="s">
+        <v>2452</v>
+      </c>
+      <c r="X130" s="11" t="s">
+        <v>2453</v>
+      </c>
+      <c r="Y130" s="11" t="s">
+        <v>2443</v>
+      </c>
+      <c r="Z130" s="11" t="s">
+        <v>2454</v>
+      </c>
+      <c r="AA130" s="11" t="s">
+        <v>2455</v>
+      </c>
+      <c r="AB130" s="11" t="s">
+        <v>2443</v>
+      </c>
+      <c r="AD130" s="11" t="s">
+        <v>2420</v>
+      </c>
+      <c r="AE130" s="11" t="s">
+        <v>2456</v>
+      </c>
+      <c r="AF130" s="11">
+        <v>0.9</v>
+      </c>
+      <c r="AG130" s="11">
+        <v>0</v>
+      </c>
+      <c r="AH130" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="AI130" s="11" t="s">
+        <v>2175</v>
+      </c>
+      <c r="AJ130" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="AK130" s="1">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="131" spans="1:37" s="11" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A131" s="1" t="s">
+        <v>2591</v>
+      </c>
+      <c r="B131" s="11" t="s">
+        <v>2457</v>
+      </c>
+      <c r="C131" s="11" t="s">
+        <v>2458</v>
+      </c>
+      <c r="D131" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="E131" s="11" t="s">
+        <v>2363</v>
+      </c>
+      <c r="F131" s="11" t="s">
+        <v>2459</v>
+      </c>
+      <c r="G131" s="11" t="s">
+        <v>2460</v>
+      </c>
+      <c r="H131" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="I131" s="8">
+        <v>46227</v>
+      </c>
+      <c r="J131" s="8">
+        <v>46227</v>
+      </c>
+      <c r="K131" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="L131" s="11">
+        <v>8</v>
+      </c>
+      <c r="M131" s="11" t="s">
+        <v>2461</v>
+      </c>
+      <c r="N131" s="11" t="s">
+        <v>2462</v>
+      </c>
+      <c r="O131" s="11" t="s">
+        <v>2463</v>
+      </c>
+      <c r="P131" s="11" t="s">
+        <v>2464</v>
+      </c>
+      <c r="Q131" s="11" t="s">
+        <v>2465</v>
+      </c>
+      <c r="R131" s="11" t="s">
+        <v>2466</v>
+      </c>
+      <c r="S131" s="11" t="s">
+        <v>2467</v>
+      </c>
+      <c r="T131" s="11" t="s">
+        <v>2468</v>
+      </c>
+      <c r="U131" s="11" t="s">
+        <v>2469</v>
+      </c>
+      <c r="V131" s="11" t="s">
+        <v>2470</v>
+      </c>
+      <c r="W131" s="11" t="s">
+        <v>2471</v>
+      </c>
+      <c r="X131" s="11" t="s">
+        <v>2472</v>
+      </c>
+      <c r="Y131" s="11" t="s">
+        <v>2461</v>
+      </c>
+      <c r="Z131" s="11" t="s">
+        <v>2473</v>
+      </c>
+      <c r="AA131" s="11" t="s">
+        <v>2474</v>
+      </c>
+      <c r="AB131" s="11" t="s">
+        <v>2461</v>
+      </c>
+      <c r="AD131" s="11" t="s">
+        <v>2420</v>
+      </c>
+      <c r="AE131" s="11" t="s">
+        <v>2475</v>
+      </c>
+      <c r="AF131" s="11">
+        <v>0.9</v>
+      </c>
+      <c r="AG131" s="11">
+        <v>0</v>
+      </c>
+      <c r="AH131" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="AI131" s="11" t="s">
+        <v>2438</v>
+      </c>
+      <c r="AJ131" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="AK131" s="1">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="132" spans="1:37" s="11" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A132" s="1" t="s">
+        <v>2592</v>
+      </c>
+      <c r="B132" s="11" t="s">
+        <v>2476</v>
+      </c>
+      <c r="C132" s="11" t="s">
+        <v>2477</v>
+      </c>
+      <c r="D132" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="E132" s="11" t="s">
+        <v>2363</v>
+      </c>
+      <c r="F132" s="11" t="s">
+        <v>2478</v>
+      </c>
+      <c r="G132" s="11" t="s">
+        <v>2479</v>
+      </c>
+      <c r="H132" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="I132" s="8">
+        <v>46227</v>
+      </c>
+      <c r="J132" s="8">
+        <v>46227</v>
+      </c>
+      <c r="K132" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="L132" s="11">
+        <v>6</v>
+      </c>
+      <c r="M132" s="11" t="s">
+        <v>2480</v>
+      </c>
+      <c r="N132" s="11" t="s">
+        <v>2481</v>
+      </c>
+      <c r="O132" s="11" t="s">
+        <v>2482</v>
+      </c>
+      <c r="P132" s="11" t="s">
+        <v>2483</v>
+      </c>
+      <c r="Q132" s="11" t="s">
+        <v>2484</v>
+      </c>
+      <c r="R132" s="11" t="s">
+        <v>2485</v>
+      </c>
+      <c r="S132" s="11" t="s">
+        <v>2486</v>
+      </c>
+      <c r="T132" s="11" t="s">
+        <v>2487</v>
+      </c>
+      <c r="U132" s="11" t="s">
+        <v>2488</v>
+      </c>
+      <c r="V132" s="11" t="s">
+        <v>2489</v>
+      </c>
+      <c r="W132" s="11" t="s">
+        <v>2490</v>
+      </c>
+      <c r="X132" s="11" t="s">
+        <v>2491</v>
+      </c>
+      <c r="Y132" s="11" t="s">
+        <v>2480</v>
+      </c>
+      <c r="Z132" s="11" t="s">
+        <v>2492</v>
+      </c>
+      <c r="AA132" s="11" t="s">
+        <v>2493</v>
+      </c>
+      <c r="AB132" s="11" t="s">
+        <v>2480</v>
+      </c>
+      <c r="AD132" s="11" t="s">
+        <v>2439</v>
+      </c>
+      <c r="AE132" s="11" t="s">
+        <v>2494</v>
+      </c>
+      <c r="AF132" s="11">
+        <v>0.9</v>
+      </c>
+      <c r="AG132" s="11">
+        <v>0</v>
+      </c>
+      <c r="AH132" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="AI132" s="11" t="s">
+        <v>2175</v>
+      </c>
+      <c r="AJ132" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="AK132" s="1">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="133" spans="1:37" s="11" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A133" s="1" t="s">
+        <v>2593</v>
+      </c>
+      <c r="B133" s="11" t="s">
+        <v>2495</v>
+      </c>
+      <c r="C133" s="11" t="s">
+        <v>2496</v>
+      </c>
+      <c r="D133" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="E133" s="11" t="s">
+        <v>2363</v>
+      </c>
+      <c r="F133" s="11" t="s">
+        <v>2497</v>
+      </c>
+      <c r="G133" s="11" t="s">
+        <v>2498</v>
+      </c>
+      <c r="H133" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="I133" s="8">
+        <v>46227</v>
+      </c>
+      <c r="J133" s="8">
+        <v>46227</v>
+      </c>
+      <c r="K133" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="L133" s="11">
+        <v>6</v>
+      </c>
+      <c r="M133" s="11" t="s">
+        <v>2499</v>
+      </c>
+      <c r="N133" s="11" t="s">
+        <v>2500</v>
+      </c>
+      <c r="O133" s="11" t="s">
+        <v>2501</v>
+      </c>
+      <c r="P133" s="11" t="s">
+        <v>2502</v>
+      </c>
+      <c r="Q133" s="11" t="s">
+        <v>2503</v>
+      </c>
+      <c r="R133" s="11" t="s">
+        <v>2504</v>
+      </c>
+      <c r="S133" s="11" t="s">
+        <v>2505</v>
+      </c>
+      <c r="T133" s="11" t="s">
+        <v>2506</v>
+      </c>
+      <c r="U133" s="11" t="s">
+        <v>2507</v>
+      </c>
+      <c r="V133" s="11" t="s">
+        <v>2508</v>
+      </c>
+      <c r="W133" s="11" t="s">
+        <v>2509</v>
+      </c>
+      <c r="X133" s="11" t="s">
+        <v>2510</v>
+      </c>
+      <c r="Y133" s="11" t="s">
+        <v>2499</v>
+      </c>
+      <c r="Z133" s="11" t="s">
+        <v>2511</v>
+      </c>
+      <c r="AA133" s="11" t="s">
+        <v>2512</v>
+      </c>
+      <c r="AB133" s="11" t="s">
+        <v>2499</v>
+      </c>
+      <c r="AE133" s="11" t="s">
+        <v>2513</v>
+      </c>
+      <c r="AF133" s="11">
+        <v>1</v>
+      </c>
+      <c r="AG133" s="11">
+        <v>0</v>
+      </c>
+      <c r="AH133" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="AI133" s="11" t="s">
+        <v>2514</v>
+      </c>
+      <c r="AJ133" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="AK133" s="1">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="134" spans="1:37" s="11" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A134" s="1" t="s">
+        <v>2594</v>
+      </c>
+      <c r="B134" s="11" t="s">
+        <v>2515</v>
+      </c>
+      <c r="C134" s="11" t="s">
+        <v>2516</v>
+      </c>
+      <c r="D134" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="E134" s="11" t="s">
+        <v>2363</v>
+      </c>
+      <c r="F134" s="11" t="s">
+        <v>2517</v>
+      </c>
+      <c r="G134" s="11" t="s">
+        <v>2518</v>
+      </c>
+      <c r="H134" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="I134" s="8">
+        <v>46227</v>
+      </c>
+      <c r="J134" s="8">
+        <v>46227</v>
+      </c>
+      <c r="K134" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="L134" s="11">
+        <v>8</v>
+      </c>
+      <c r="M134" s="11" t="s">
+        <v>2519</v>
+      </c>
+      <c r="N134" s="11" t="s">
+        <v>2520</v>
+      </c>
+      <c r="O134" s="11" t="s">
+        <v>2521</v>
+      </c>
+      <c r="P134" s="11" t="s">
+        <v>2522</v>
+      </c>
+      <c r="Q134" s="11" t="s">
+        <v>2523</v>
+      </c>
+      <c r="R134" s="11" t="s">
+        <v>2524</v>
+      </c>
+      <c r="S134" s="11" t="s">
+        <v>2525</v>
+      </c>
+      <c r="T134" s="11" t="s">
+        <v>2526</v>
+      </c>
+      <c r="U134" s="11" t="s">
+        <v>2527</v>
+      </c>
+      <c r="V134" s="11" t="s">
+        <v>2528</v>
+      </c>
+      <c r="W134" s="11" t="s">
+        <v>2529</v>
+      </c>
+      <c r="X134" s="11" t="s">
+        <v>2530</v>
+      </c>
+      <c r="Y134" s="11" t="s">
+        <v>2519</v>
+      </c>
+      <c r="Z134" s="11" t="s">
+        <v>2531</v>
+      </c>
+      <c r="AA134" s="11" t="s">
+        <v>2532</v>
+      </c>
+      <c r="AB134" s="11" t="s">
+        <v>2519</v>
+      </c>
+      <c r="AE134" s="11" t="s">
+        <v>2533</v>
+      </c>
+      <c r="AF134" s="11">
+        <v>1</v>
+      </c>
+      <c r="AG134" s="11">
+        <v>0</v>
+      </c>
+      <c r="AH134" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="AI134" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="AJ134" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="AK134" s="1">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="135" spans="1:37" s="11" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A135" s="1" t="s">
+        <v>2595</v>
+      </c>
+      <c r="B135" s="11" t="s">
+        <v>2534</v>
+      </c>
+      <c r="C135" s="11" t="s">
+        <v>2535</v>
+      </c>
+      <c r="D135" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="E135" s="11" t="s">
+        <v>2363</v>
+      </c>
+      <c r="F135" s="11" t="s">
+        <v>2536</v>
+      </c>
+      <c r="G135" s="11" t="s">
+        <v>2537</v>
+      </c>
+      <c r="H135" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="I135" s="8">
+        <v>46227</v>
+      </c>
+      <c r="J135" s="8">
+        <v>46227</v>
+      </c>
+      <c r="K135" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="L135" s="11">
+        <v>7</v>
+      </c>
+      <c r="M135" s="11" t="s">
+        <v>2538</v>
+      </c>
+      <c r="N135" s="11" t="s">
+        <v>2539</v>
+      </c>
+      <c r="O135" s="11" t="s">
+        <v>2540</v>
+      </c>
+      <c r="P135" s="11" t="s">
+        <v>2541</v>
+      </c>
+      <c r="Q135" s="11" t="s">
+        <v>2542</v>
+      </c>
+      <c r="R135" s="11" t="s">
+        <v>2543</v>
+      </c>
+      <c r="S135" s="11" t="s">
+        <v>2544</v>
+      </c>
+      <c r="T135" s="11" t="s">
+        <v>2537</v>
+      </c>
+      <c r="U135" s="11" t="s">
+        <v>2545</v>
+      </c>
+      <c r="V135" s="11" t="s">
+        <v>2546</v>
+      </c>
+      <c r="W135" s="11" t="s">
+        <v>2543</v>
+      </c>
+      <c r="X135" s="11" t="s">
+        <v>2547</v>
+      </c>
+      <c r="Y135" s="11" t="s">
+        <v>2538</v>
+      </c>
+      <c r="Z135" s="11" t="s">
+        <v>2536</v>
+      </c>
+      <c r="AA135" s="11" t="s">
+        <v>2548</v>
+      </c>
+      <c r="AB135" s="11" t="s">
+        <v>2538</v>
+      </c>
+      <c r="AE135" s="11" t="s">
+        <v>2549</v>
+      </c>
+      <c r="AF135" s="11">
+        <v>0.9</v>
+      </c>
+      <c r="AG135" s="11">
+        <v>0</v>
+      </c>
+      <c r="AH135" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="AI135" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="AJ135" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="AK135" s="1">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="136" spans="1:37" s="11" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A136" s="1" t="s">
+        <v>2596</v>
+      </c>
+      <c r="B136" s="11" t="s">
+        <v>2550</v>
+      </c>
+      <c r="C136" s="11" t="s">
+        <v>2551</v>
+      </c>
+      <c r="D136" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="E136" s="11" t="s">
+        <v>2363</v>
+      </c>
+      <c r="F136" s="11" t="s">
+        <v>2552</v>
+      </c>
+      <c r="G136" s="11" t="s">
+        <v>2553</v>
+      </c>
+      <c r="H136" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="I136" s="8">
+        <v>46227</v>
+      </c>
+      <c r="J136" s="8">
+        <v>46227</v>
+      </c>
+      <c r="K136" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="L136" s="11">
+        <v>6</v>
+      </c>
+      <c r="M136" s="11" t="s">
+        <v>2554</v>
+      </c>
+      <c r="N136" s="11" t="s">
+        <v>2555</v>
+      </c>
+      <c r="O136" s="11" t="s">
+        <v>2556</v>
+      </c>
+      <c r="P136" s="11" t="s">
+        <v>2557</v>
+      </c>
+      <c r="Q136" s="11" t="s">
+        <v>2558</v>
+      </c>
+      <c r="R136" s="11" t="s">
+        <v>2559</v>
+      </c>
+      <c r="S136" s="11" t="s">
+        <v>2560</v>
+      </c>
+      <c r="T136" s="11" t="s">
+        <v>2561</v>
+      </c>
+      <c r="U136" s="11" t="s">
+        <v>2562</v>
+      </c>
+      <c r="V136" s="11" t="s">
+        <v>2563</v>
+      </c>
+      <c r="W136" s="11" t="s">
+        <v>2564</v>
+      </c>
+      <c r="X136" s="11" t="s">
+        <v>2565</v>
+      </c>
+      <c r="Y136" s="11" t="s">
+        <v>2554</v>
+      </c>
+      <c r="Z136" s="11" t="s">
+        <v>2566</v>
+      </c>
+      <c r="AA136" s="11" t="s">
+        <v>2567</v>
+      </c>
+      <c r="AB136" s="11" t="s">
+        <v>2554</v>
+      </c>
+      <c r="AE136" s="11" t="s">
+        <v>2568</v>
+      </c>
+      <c r="AF136" s="11">
+        <v>0.9</v>
+      </c>
+      <c r="AG136" s="11">
+        <v>0</v>
+      </c>
+      <c r="AH136" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="AI136" s="11" t="s">
+        <v>2175</v>
+      </c>
+      <c r="AJ136" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="AK136" s="1">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="137" spans="1:37" s="11" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A137" s="1" t="s">
+        <v>2597</v>
+      </c>
+      <c r="B137" s="11" t="s">
+        <v>2569</v>
+      </c>
+      <c r="C137" s="11" t="s">
+        <v>2570</v>
+      </c>
+      <c r="D137" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="E137" s="11" t="s">
+        <v>2363</v>
+      </c>
+      <c r="F137" s="11" t="s">
+        <v>2497</v>
+      </c>
+      <c r="G137" s="11" t="s">
+        <v>2571</v>
+      </c>
+      <c r="H137" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="I137" s="8">
+        <v>46227</v>
+      </c>
+      <c r="J137" s="8">
+        <v>46227</v>
+      </c>
+      <c r="K137" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="L137" s="11">
+        <v>5</v>
+      </c>
+      <c r="M137" s="11" t="s">
+        <v>2443</v>
+      </c>
+      <c r="N137" s="11" t="s">
+        <v>2572</v>
+      </c>
+      <c r="O137" s="11" t="s">
+        <v>2573</v>
+      </c>
+      <c r="P137" s="11" t="s">
+        <v>2574</v>
+      </c>
+      <c r="Q137" s="11" t="s">
+        <v>2575</v>
+      </c>
+      <c r="R137" s="11" t="s">
+        <v>2576</v>
+      </c>
+      <c r="S137" s="11" t="s">
+        <v>2577</v>
+      </c>
+      <c r="T137" s="11" t="s">
+        <v>2578</v>
+      </c>
+      <c r="U137" s="11" t="s">
+        <v>2579</v>
+      </c>
+      <c r="V137" s="11" t="s">
+        <v>2580</v>
+      </c>
+      <c r="W137" s="11" t="s">
+        <v>2581</v>
+      </c>
+      <c r="X137" s="11" t="s">
+        <v>2582</v>
+      </c>
+      <c r="Y137" s="11" t="s">
+        <v>2443</v>
+      </c>
+      <c r="Z137" s="11" t="s">
+        <v>2583</v>
+      </c>
+      <c r="AA137" s="11" t="s">
+        <v>2584</v>
+      </c>
+      <c r="AB137" s="11" t="s">
+        <v>2443</v>
+      </c>
+      <c r="AE137" s="11" t="s">
+        <v>2585</v>
+      </c>
+      <c r="AF137" s="11">
+        <v>1</v>
+      </c>
+      <c r="AG137" s="11">
+        <v>0</v>
+      </c>
+      <c r="AH137" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="AI137" s="11" t="s">
+        <v>2514</v>
+      </c>
+      <c r="AJ137" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="AK137" s="1">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="138" spans="1:37" s="11" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A138" s="1"/>
+      <c r="I138" s="8"/>
+      <c r="J138" s="8"/>
+      <c r="AK138" s="1"/>
+    </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="AB109:AD109"/>
-    <mergeCell ref="AB110:AD110"/>
-    <mergeCell ref="AB103:AD103"/>
-    <mergeCell ref="AB104:AD104"/>
-    <mergeCell ref="AB105:AD105"/>
-    <mergeCell ref="AB106:AD106"/>
-    <mergeCell ref="AB107:AD107"/>
-    <mergeCell ref="AB108:AD108"/>
     <mergeCell ref="AB102:AD102"/>
     <mergeCell ref="AB91:AD91"/>
     <mergeCell ref="AB92:AD92"/>
@@ -21641,6 +23656,14 @@
     <mergeCell ref="AB99:AD99"/>
     <mergeCell ref="AB100:AD100"/>
     <mergeCell ref="AB101:AD101"/>
+    <mergeCell ref="AB109:AD109"/>
+    <mergeCell ref="AB110:AD110"/>
+    <mergeCell ref="AB103:AD103"/>
+    <mergeCell ref="AB104:AD104"/>
+    <mergeCell ref="AB105:AD105"/>
+    <mergeCell ref="AB106:AD106"/>
+    <mergeCell ref="AB107:AD107"/>
+    <mergeCell ref="AB108:AD108"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <hyperlinks>
@@ -22296,6 +24319,54 @@
     <hyperlink ref="Y110" r:id="rId650" xr:uid="{D4F9381A-0A91-4DC9-9EE0-53B5D5C3815C}"/>
     <hyperlink ref="AB110" r:id="rId651" xr:uid="{9F9932CD-05A0-4240-8745-A3A4A7F3881C}"/>
     <hyperlink ref="AE110" r:id="rId652" xr:uid="{6D88C61F-5BF3-489A-8ADB-5F7021459E0C}"/>
+    <hyperlink ref="M126" r:id="rId653" xr:uid="{F9F216DB-C4D2-498F-ADD6-C096FB5928CA}"/>
+    <hyperlink ref="V126" r:id="rId654" xr:uid="{09625B4B-AE75-4E5A-98AF-4C0443DD4DEF}"/>
+    <hyperlink ref="Y126" r:id="rId655" xr:uid="{317AAAEB-8C66-487F-8988-65A1CDFB6B92}"/>
+    <hyperlink ref="AB126" r:id="rId656" xr:uid="{077031BB-95D7-4183-841C-4DC6A39D924F}"/>
+    <hyperlink ref="M127" r:id="rId657" xr:uid="{8EAAFDC1-D510-49B1-8029-8A37F7CF548B}"/>
+    <hyperlink ref="V127" r:id="rId658" xr:uid="{144CEF9B-8CE3-4C83-9FBD-13F4B9878C52}"/>
+    <hyperlink ref="Y127" r:id="rId659" xr:uid="{9F96E644-B9CF-4DD2-BA72-D5BFAEFA6405}"/>
+    <hyperlink ref="AB127" r:id="rId660" xr:uid="{D0821501-3427-480E-AFF3-DA88BF2B7F74}"/>
+    <hyperlink ref="M128" r:id="rId661" xr:uid="{ABD7E8F9-300C-4079-BED5-A9FB9749CAB4}"/>
+    <hyperlink ref="V128" r:id="rId662" xr:uid="{A3506AE7-9CC9-4FCB-BE7A-AC3C42C19B82}"/>
+    <hyperlink ref="Y128" r:id="rId663" xr:uid="{035338E5-324D-4FB1-9B53-033F746C4426}"/>
+    <hyperlink ref="AB128" r:id="rId664" xr:uid="{E78C99F5-EDA7-4E54-8864-1D1125B363CF}"/>
+    <hyperlink ref="M129" r:id="rId665" xr:uid="{36554DCC-698C-4ECD-B04C-C8CB8461A3C2}"/>
+    <hyperlink ref="V129" r:id="rId666" xr:uid="{C0F597EA-E142-4E75-B1C4-80ED75657A9D}"/>
+    <hyperlink ref="Y129" r:id="rId667" xr:uid="{1E5F03A2-4EBB-43B1-92D3-509F0F6CBE53}"/>
+    <hyperlink ref="AB129" r:id="rId668" xr:uid="{0081A48D-545F-4202-8CD0-780385F6CA41}"/>
+    <hyperlink ref="M130" r:id="rId669" xr:uid="{C875D95D-BBF5-4B3E-9751-DB26F38E71A1}"/>
+    <hyperlink ref="V130" r:id="rId670" xr:uid="{50C1D257-26C9-46B0-AA28-901CC8A0D341}"/>
+    <hyperlink ref="Y130" r:id="rId671" xr:uid="{8E951209-095C-4ECC-B119-42836B74F902}"/>
+    <hyperlink ref="AB130" r:id="rId672" xr:uid="{9806FB06-9804-49F8-9B85-5C9C0172F951}"/>
+    <hyperlink ref="M131" r:id="rId673" xr:uid="{F7CFF534-ACF2-4509-8FD7-7D5349DACAA9}"/>
+    <hyperlink ref="V131" r:id="rId674" xr:uid="{59D5211A-971D-4D3B-8C64-92165610BE4D}"/>
+    <hyperlink ref="Y131" r:id="rId675" xr:uid="{DF0FEDFB-B6C7-49F5-984D-A7ADC2DF4701}"/>
+    <hyperlink ref="AB131" r:id="rId676" xr:uid="{777AA692-620C-4D8F-8BEC-B517C131C539}"/>
+    <hyperlink ref="M132" r:id="rId677" xr:uid="{476F1A8F-F3EE-4570-94F2-B96D31C1BA4B}"/>
+    <hyperlink ref="V132" r:id="rId678" xr:uid="{E80008CB-173E-437F-AF97-D8E7D3D4B4DC}"/>
+    <hyperlink ref="Y132" r:id="rId679" xr:uid="{BC9BC0D3-2833-44EC-9AA3-7679760D6BFB}"/>
+    <hyperlink ref="AB132" r:id="rId680" xr:uid="{E607CB1A-01BC-4515-846B-C35BB2AE8948}"/>
+    <hyperlink ref="M133" r:id="rId681" xr:uid="{0F313E6E-FB12-400B-B7DE-65FC465FEE74}"/>
+    <hyperlink ref="V133" r:id="rId682" xr:uid="{7BA47852-C742-420B-8059-095CCBEE0168}"/>
+    <hyperlink ref="Y133" r:id="rId683" xr:uid="{72F92A4D-0A58-47A6-A007-6FC0594B7D6C}"/>
+    <hyperlink ref="AB133" r:id="rId684" xr:uid="{34671A43-8361-414F-BDE5-DBFDB34E20F2}"/>
+    <hyperlink ref="M134" r:id="rId685" xr:uid="{B99C3A8E-818C-487D-B666-71AB0DB321A8}"/>
+    <hyperlink ref="V134" r:id="rId686" xr:uid="{712DA704-7C1C-4955-9974-ADBA49688A2A}"/>
+    <hyperlink ref="Y134" r:id="rId687" xr:uid="{3425F990-4F0E-4C98-8CA2-1219BB2BCE2D}"/>
+    <hyperlink ref="AB134" r:id="rId688" xr:uid="{6B41168C-C520-4203-9BF2-CE0D1A9C242F}"/>
+    <hyperlink ref="M135" r:id="rId689" xr:uid="{29C9CD95-46A4-42ED-BC3A-354609F7C3CD}"/>
+    <hyperlink ref="V135" r:id="rId690" xr:uid="{87A8ECD1-3464-4920-9F21-5AA291013D60}"/>
+    <hyperlink ref="Y135" r:id="rId691" xr:uid="{331FE4F9-DF7A-4E7E-AE66-4FA1148BED67}"/>
+    <hyperlink ref="AB135" r:id="rId692" xr:uid="{122AACD0-3B38-4D03-A5D6-0E6247FB6B45}"/>
+    <hyperlink ref="M136" r:id="rId693" xr:uid="{C601C2C7-1327-4D7D-8035-475976A47DAA}"/>
+    <hyperlink ref="V136" r:id="rId694" xr:uid="{3570BDA8-DCB9-4BC3-9D6C-96F37EF49D03}"/>
+    <hyperlink ref="Y136" r:id="rId695" xr:uid="{06226498-27F8-4C08-96EF-E6E907F2F03F}"/>
+    <hyperlink ref="AB136" r:id="rId696" xr:uid="{E625964F-5ADA-4CEC-8A34-EE4B8B4A1DD2}"/>
+    <hyperlink ref="M137" r:id="rId697" xr:uid="{31841A9A-9D8F-4FD0-AABD-99997835915C}"/>
+    <hyperlink ref="V137" r:id="rId698" xr:uid="{49F2353F-D616-4F25-861F-AF64C36AB4EA}"/>
+    <hyperlink ref="Y137" r:id="rId699" xr:uid="{DEF76E2E-8DE6-4C08-8EA5-50575EB3F513}"/>
+    <hyperlink ref="AB137" r:id="rId700" xr:uid="{2DDEFAF8-B7EB-4330-8A06-588971A760F7}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
